--- a/visitors.xlsx
+++ b/visitors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,34 +663,82 @@
           <t>wfdg</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>6374532706</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>parthipancseai@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>uytuy</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>yufyf</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAc4AAAC4CAYAAABq6gzYAAAQAElEQVR4AeydB3wUVRfFz4YOKr18WLCLgqCAUoUgHRIIvXdFQJqACoQivUkvAalC6EWkFwkIiHQF6UWaQCjSmxT59t7NroghbJItM7snP+fOzJuZ9+78X+TktTsBD+5cfcCNDPg7wN8B/g7wd4C/A879DgSAPyRAAiRAAiRAAk4ToHA6jcoDN7IIEiABEiABwxOgcBq+iuggCZAACZCAkQhQOI1UG/TFSAToCwmQAAlES4DCGS0WJpIACZAACZBA9AQonNFzYSoJkICRCNAXEjAQAQqngSqDrpAACZAACRifAIXT+HVED0mABEjASAT83hcKp9//ChAACZAACZBAbAhQOGNDi/eSAAmQAAn4PQFDCaff1wYBkAAJkAAJGJ4AhdPwVUQHSYAESIAEjESAwmmk2jCUL3SGBEiABEggOgIUzuioMI0ESIAESIAEHkOAwvkYMEwmASMRoC8kQALGIUDhNE5d0BMSIAESIAETEKBwmqCS6CIJkICRCNAXfydA4fT33wC+PwmQAAmQQKwIUDhjhYs3kwAJkAAJGImAN3yhcHqDOsskARIgARIwLQEKp2mrjo6TAAmQAAl4gwCF83HUmU4CJEACJEAC0RCgcEYDhUkkQAIkQAIk8DgCFM7HkWG6kQjQFxIgARIwDAEKp2Gqgo6QAAmQAAmYgQCF0wy1RB9JwEgE6AsJ+DkBCqef/wLw9UmABEiABGJHgMIZO168mwRIgASMRIC+eIEAhdML0FkkCZAACZCAeQlQOM1bd/ScBEiABEjACwQeK5xe8IVFkgAJkAAJkIDhCVA4DV9FdJAESIAESMBIBCicRqqNx/rCCyRAAiRAAkYhQOE0Sk3QDxIgARIgAVMQoHCaopropJEI0BcSIAH/JkDhdGP9//333zh/4QL2HzqEjVu3YuHy5Rg5YSLqNGuO75Yuw4MHD9xYOrMmARIgARJwBwEKZzyprohYg3rNW+CzLl3xSdv2qNywMYqGVESOIoF4MVce5C5eEiWrVkeNjz9Biw6dMGDESKz7eRNadwpFkfIhGDc1HNev34inF3ycBPyVAN+bBDxPgMIZR+Y7dv2mIvlx23ZYu3Ej5i1ajGUREdj6yy84cuw4Ll+5+p+cU6V8BpkypEeiRAn12rGTJ9Fz0GC8W6w42nXthj0HDmg6DQmQAAmQgHEJBBjXNWN6tnvfftRu1gwh9eqrSIqXAQEByJMzJ2pXqYw2nzRB9y+/wMh+fTBjbBhWzpmF7T+sxLEd27Drx7XYsnIF9m/8CUN790LunDnkcfz111+Ys3ARylSviYr1G2g37t27d/UaDQmQAAmYhYC/+BngLy8a3/c89PvvaNK2PcrWrIX1P2/W7JIkSYKP69bBjtU/YP63k9C3cyjaNmuKhjVroHzp0iiYNy+yvvYa0qdLBxFXfchqEiVKhErlyuK7byersNaoGIJkSZNarwDbd+7Sbtz3S5VGf2u37umzkZpOQwIkQAIkYAwCFM4n1IN0p7bs0BElqlTDcmtXrNyeMGFC1K1WFT8tXoQu7doiTepUkhynTYR1QLeu2Lpqheb1/LOZNZ8/L17CqAkTkb90OZSoXBU79+zVdBoSIAESIAHvEjCHcHqB0anISHz+VXcUDamE75evgMyQTZAgAaqWD8b6xQvRu1NHZEifzmWePfP009p63WAV4/Cw0ShRpIi2UmXm7YEjR/BJu/YuK4sZkQAJkAAJxJ0AhfMRdn9evIguffujcHAFzFrwPe7fvw+LxaJdr2sWzMegHt3xbKZMjzzlulOLxYLC+fNhwrAh2LhsMfLlyaOZn7YK+eGjR/WYhgRIgARIwHsEKJxR7GUWbO8hQ5G/bBC+nTUL9sk5JQMD8cO8OTrZ58Xnn4+62zO7zBkzYeKwoUgaNf4ZNmmyZwqOuRReJQESIAG/JuD3wilrKAeNDkOBsmUx9tspuH37tv5CSKtv2czpGD90MF57+WVN84Z5KkVy1K1aRYv+bslSnD1/Xo9pSIAESIAEvEPAb4XzllUgdfJN2XIY9s04XL9xU2sgV463sWDKt5BxxmxZs2qat02TenWR0Dq+es/abSwBE7ztD8s3EAG64jQBCTwyeuIkXPjzT6ef4Y0kEB0BvxPOO3fuYHz4NGsLM0iXe1y5agtUkDNbNhVLEU0Rz+hgeSstY/r0CLG2iKX86fPmOURezrmRAAnETGDXnn0oWC5IQ132Gz4CvaxDMjE/waskEDMBvxHOe/fuIXzOXBQKKo8eXw+CTAISNLIcRLpjF02bqpNyJM2IW4uPGukkJWkZT7GOwRrRR/pEAkYiIDPhJ8+chYr16+PkqdPqWvJkSVElKEiP3WCYpZ8Q8HnhlFmxcxctQpEKIejUuw8iz53Tqn05Sxad8LNi9kzIBCBNNLARf4t+UFA9HBce7pi8pAk0JEAC/yIgITHL1qiFrv364671j2aL9WqZ4sWwaflyFMqX13rG/0gg7gR8Vjhl/ePilStRvHJVtO3SzfEX53OZ/4evu3+F1fPnQqL7WCzyv1TcAXryyWb1G2hxf168hLmLFusxDQmQwD8ETpw8hQp16yGkXn3sPXhQL3yQPy/WLlyAsV8PRKqUz2gajR8QcOMr+qRw/rBuncZ9bf5FBxw5dkzxyThhr44dsG7h96hWoTwkmIFeMJHJmzsXcrz1lnosM4DljwM9oSEBPydg75b9sFIl/PLbbqXxvwwZMebrAZgWFoaXXnhB02hIwBUEfEo4JSxdvjJl0ahVG8dfm6lTpUTntp9pSLt61atBwuW5Apy38vjUOtYpZf9+/DhWrFkjh9xMREDG2qfMmoMqDRujc5++kLXDnfv21fPwuXM14IaJXscQrj7cLXvn7l1IH1K5ksWxbtEClC1e3BA+0gnfIuAzwiljmbWbNsPpM5FaQ7L+8cuWLaxjGssgyzk00SXGu5mULloU0t0sXowcP1F23ExA4LslS1CuZm28XbgIRCi3/PILpsyeo2uHRUjlvFOvPnivZGn91Jx8hccEr+VVF0+c/APl69SNtls2bMAAyEcYvOogC/dZAj4jnPKP0NVr17SiihcpooL5aeNGjq+O6AUfMBaLBS0+aqxvsmvvXixZ9YMe0xiTwObtO1CgbDm0Du2C3/btw42bt9RR6fnIlCGDdiHKMELChAk0XdYYylpd+QpPsUpVIOsOz5w7q9do/iEwf8lSfGjl8+vuPZrIblnFQOMhAj4hnBcvXcbAkSMVmazHnDhsCCRouib4oKkaHOz4a3rAiBE++IbOv5KR79x36CCkF+SP02fUTYvFgnLWrsPvp07B79u2YMvK5fhx4QIdRji8ZTNmjA1DFWvdpkieTO+XT9nJukP5Qk6NJk0xZ+Eih/DqDX5ozl+4gAatWqFNaGfcuXtHu2XLFCvKblk//F3w5iv7hHD2HDxYgwJYLBYM+KqLN3l6pGz5nue7b2fXsv5+oDsagxHYvH07KtRpYP3H3TbmFlyqJHauXYOwrwfAXncPuyzfa5Xvtw7u2R2/RKyG7IsUyK9fyJGJLxu3bEG7rt2QM/BDlK5WXT9AYA8P+XA+vnxsb2VGrNugr/nKi1mwePo0jB00yPGHpF6gIQE3EzC9cG779VfMi1qaUb96Nbz52utuRgaMGD8BVRt/hInTZri9rMcVkDdXLr106/Yt3dMYi0CjNm1x+y9b3OOhfXpjVP9+Ti+FkKD+0vKcOnoUtv+wEl3bt4M9/OOdO39h78FD+sm7bB8U0dbXVOtYqXTxep+A6z2QyVQLl61AYEhFbWVKpC+LxYLmjRpi5ZzZePutN11fKHMkgScQMLVwyoSg0N799BXTpE6FL1q21GN3m6lz5kLGrkZOnODuoh6bv4yPycXzF/4El6UICeNsyyMicC1qvL16hQqoWLZMnJ1LmyYNPqpTG/LBgYjv5iGoZAkkSpgI8iNf8JHWV2ifvshVrASCatXB4LAxkLFvuW7WTcRy9br1uv46R5FAtOjYEb8fO66vI4FAFoZPQYdWLSE9L5pIQwIeJmBq4ZTZiDKOJMxCP/sMMpNWjt29PZspoxZx6fIVSOB1PfGwsQuniGbk+XMeLp3FxURgwIhRejl1qpTo1amDHrvCvPrSSxg9oD+ObNuMNQvmI/SzNng/17vanSv5i2AOHfuNCug7RT+EBAKYv3SJKZa4iFhGWLtgW3cKhYhlw1atIRG/JMSkvFuAtZUZXKoUVs2dDZnHIGncYibAq+4jYFrh1AlBo/6ZEFS1fLD7KD2Sc0trN60kSYt3527bYms59+QmMzHt5UWe5afG7Cy8vV9mbW0ePnpU3WjRuLHbxt5eefFFfFK/HuZaez1++3Ethvfto5Gw7JPi5P8PCQTQplMXwy5xsYtl2y7d8E7RYtrt/N3SZTpfQQDKsit5R4kjfeyX7dbu7r5sZQoYbl4nYFrh9OaEoLx5cjv+yo9Yb5uo4OmazJQhvaNItjgdKLx+MPCh1ma9alU94s/TTz+FkDKlMbJfH/y6NgIzvxmDUkWLIkGCAC1fxj+NsMRFekckcId8pKBczVq6plVmyErL0r6UTHpSmjaoh4XhU7HR2lqWVjVbmFqNNAYiYPs/KzYOGeDenXv2eHxC0MOvLcsFUj3zjCbNW7xE9542MvaVMEECLTby7Dnd03iXgKdamzG9pfxOFHj/fYwbMghHtm7x2hIXu0guWLZcoyNV++hjZCv0AQIrVETnvv3x2779jqU1D7csZYlOpzZt8E72bDG9Jq+RgFcJmE44pXv0i696KjRPTgjSAh8y7+fOpWenIyNx7ORJPfaksVgssHfX2r/44snyWdZ/CXijtflfL/5JCQgIQMG8eXVpS8xLXIpCgi106NlbRU7CAMZlkxCC5evUQ1DtOg6RbNWxEySu8qZt2x1dsAkCAiATnEoEFoGsaWXLEvwxGQHTCae3JgQ9Wq99OnWE/HUv6ZNnzpSdx7dMGTNomWejPpWmJzReIWCE1mZMLx7zEpc7kGAL0+fNU5EToYvLJtG7frWO+e/as9chkjLzVZaM1K5SGf26dsbSGdNxaMsmneA0YeiQaNe0xvQevEYCRiBgKuGUCQ8DvTQh6NHKSpc2LYJLldTk2d8vxK3btjV7muAhkzF9Bi0p8hwnBykILxqjtTZjQiHd/A8vcSlSoIC2ADNnzKghAF964YU47dOnTYNkSZIiX57c6NclFIunh+PAzz9hyfRp6Ns5FLUqVUL2N7Oa/kMLMbHlNf8gYCrh9OaEoOh+HZrUr6fJ16/f0EgueuJBkymjbYJQJFucHqT+36Imz5oFnUlrveTOmbTW7F3+nyxxmTp6pLYAN61YpiEAJQxgXLbtq3/Agc0bMXv8ONSqXFk/gScxeV3uNDMkAS8TMI1wLlyx3KsTgqKrp2xvvOHoaho/NdzjgQgypc+obp05e1b3NNETkMg6EjS93qctULJqNSxZtSr6G+OQKuPbvb4erE8mTpwInppJ75mKYwAAEABJREFUqwXSkAAJeIWAaYSzz+BhCihxokTwVIQgLfAJpkHNmnrHiVOn8P2yFXrsKZMpYwYtSrqJr127rsc0NgIz5i/QCS/yGS+JrLN7336s/Wkj9h86rBFpDhw+bLsxHlaGDuo2+1Tj0Uo2DWrUcNu6TcmfW6wI8GYScBsB0whnWuuYolB4643XPRYhSMp70hZcsgSSJE2it/UbPlz3njKZ0tu6aqU8ruUUClBxLFuzNr7s0UMnvFy5ek0vyESu5CmS67H8odGgRSvERzwlwHqj1q1x/I8/NE+Jndq57Wd6TEMCJODbBALM8noZ06VTV9OlSat7oxgZwymQ5z1159yFC/BkCD57i1MKj2T0IKzZ8BNEzHbv2ydIYAmw4P1338X0MWH4fftW7P9pg87slIunIiMRUrd+nLpt5WslrTp1xo5dv0lWCC5VSmOn6gkNCZDAfwn4WIpphNPI3OtXq6buSQixnbv36LEnzHOZMzuK8ecWp/yx0nfYMNRv0RL37t0HLBZUKR+MPevXY+6kCSiULy/sPzKzU5ZFyPmNW7fQJrRLrFuePQYNggRylzzy5s6FYb17yiE3EiABPyFA4XRBRUsIPovFojlt2rZN954w0v2YMiqCUaSfThDad+AgAiuEIGzSt4o8d84c2LxiKQb36P7YLn0Rz0pB5fT+v+7cQdVGH2Hzju1w5mdC+HTH5+QkXuwkq2BLr4Mzz/IeEiAB3yBgcuE0RiVICL6337R9F/BnDwqnvH3a1Glkh8PHjunen8y6nzchuE5dnPjjlL52s4b1MWfiBPwvg222sSY+xgzt1dPRbXv56lXUbNIU85csfczdtmRpZcqSKDmTdbwzvhmDp55KIafcSIAE/IgAhdNFlZ3/vTya06btOyBdh3riAXPj1g0tZfuvO3XvD0b49h02HHWaNdcZrRaLBR1at0TH1q0d0Zyc4SAtz+oVQ/RW6eJtE9oZ+cuWw7qNmzRNjD3m6qiJE9H8iy8h45vJkyVFeNgoSEByuYcbCZCAfxGgcLqovvPntgnnHWvXnyfHOdOmSq1vkCljRt1703ii7HPnL6BC3XrWrtnJWpyEc9u6cgWaN2yo57E1A7t1hXy26uUsWfTRU6fPoE7z5igaUglla9ZyxFztP3wkRFwtFgvCBg7EW6+/rvfTkAAJ+B8BCqeL6txr45wJE+obvJzlBd37spGu2WKVq+C3vftgsVggn5+SIOEZ0ttmXMf13eWzVavmzkahfPkA21A1jhw7Bln7ef3GTchPggQJkCRxYjSqVRNFCxUEf0iABPyXAIXTRXXvrXHOGzdt/7AnT57MRW9ivGyka7bP0KGo2/xTXLGOR8qEqKmjR0E+PyUTpFzhsQQjnz5mNPZu2IBSHwZChPK9d991xFw9tPlnDU7e7fP2rijOA3mwCBIgAXcRoHC6kKw3xjlv3rylb5AiuW9OUrF3zY6ZPEVDGkrX7Op5c1E4v7V1qG/uWvNUiuQYN3gwjm7finmTJjDmqmvxMjcS8AkCFE4XVqM3xjlv3LK1OFMk870Wp7u6Zl1Y5cyKBJwiwJt8iwCF04X1KeOciBokm7twITzxc/2GbVZtCmtLyRPleaIMT3TNeuI9WAYJkIBvEqBwurBeZZzz6aeSa44RG37SvTvNX3/9BVkeIWWkSG4rV47NvO09cACB5UNg75rNleNtrJw7y21ds2ZmRd9JgATiQiD+z1A448/wXznkj4pbe+HiRYeo/esGF57ciBrflCyT+4Bwbti0GeXr1IN8aUbeqVnDBpg7aaJTAQ3kfm4kQAIk4AkCFE4XU27aoJ7mePfuXcgYnZ64ydy8ZZsYJNmnSGbeFqcEGRj2zTjUatrMEdDgy5afomPrVrEKaCAcuJEACZCAuwlQOF1HWHPK8847SJvGFpRg3c8/a5q7zI2btvFNyT+FSZejXLt2HbWbNceg0WHyGsj62mvYuGwJPm3cWM9pSIAESMBoBEwjnPbW1R1rS85oEB/1p7AspLcmurvFaV+cby0KZpwctP/QIZSsWg3SRSvvEFKmNBZPm4pnM2WSU24kQAIkYEgCphFOieQiBHfs2uX2sUMpJz5b4fz59fGDR47g6IkTeuwOY1/DKXmnMNk6zgXLliOodl3IdzETJ06Mvp1DMbxvH8ixvE+8N2ZAAiRAAm4iYBrhLPDee4pAll8sWLpMj41qCj+0ON+d3bX2AO/CwZPrOJesWoUi5UPwQVB53cu5+ODMJmO/HXr0QquOnSBxfSVQ+vdTJqN2lcrOPM57SIAESMDrBEwjnIN7dsdzmf+nwPoNH4F79+7psRFN+nTpIMsoxLeHv7Qh567cHm5xJvfQrNoVERFo2TFUW9LH//hD9y2tIvi4P2YuXb6CvQcPYs2GnzBm0mTkLxuE6fPnK4aCefNixexZyJY1q57T+CwBvhgJ+BQB0winxA7t3K6two88dw7jw6frsVFN4aju2nWbNrmta/lGVJxaYZAsaVLZuX1r1627448WS4Dt1+fevfto1SkUxStXQ4OWrVCjSVNtib6erwByBhZF6Wo1UL9FS/QZNhznzp9XH1s1+QjTwkYhdaqUek5DAiRAAmYhYPuXzyTeli1WDNnftLVOho8fh+vX/5lVarRXKBzVXStBCtw1Scg+OUjiq3ri/Q8cPoybt21LYJInS4bjO7YhuHQpR9EHjxxGxPoN2Lhli7ZEb9++7bgmwdhTpUwJCabe5pMmaN+8OQKihNdxEw9IgATcT4AlxJuAqYRT3rZnhy9lp6I59Jtv9NiIJo8HlqXctMep9cDEoM3bd6Byw8a4d9fWRV662IeKfVS/vtj70wZUKR+MBAkTIMdbb6FZw/r46vPPMXbw11gYPhVbV63AkW1bsOvHNTiydTPaNmuqz9KQAAmQgBkJmE44c+fMiZKBgcp64vQZkG5bPTGgcfeyFHtXbQoPjG82adcOV69dU8r9unbG0F499ViMtHgH9+iOo9u2YvH0cHRs3RqNatdEmQ8/xDvZsyFj+vSwWKI+dCkPcCMBEiABExNwoXB6jkKnz1ojQYIEuHfvHvoOHea5gmNZUuGocc6DblqWYp8clNzNwQ9kycilK1f07UPKlkGtSpX0mIYESIAE/JGAKYXz5SxZUD0kROvru6XLIGNvemIwUzhqnFPcWrRypexcup05e1bzC3Bza276vPnAA+gay35dumiZNCRAAiTgrwRMKZxSWZ9/2gxJkiSRQ3TrP1D3RjOyLCVNalv4vWlz5rncvf2HD2uekedsM1X1JMq4aidfX5n53QLNrqK1tZk8mWdm72qBNCRAAiRgQAKmFc60adKgaf16inTj1q34caN748JqQXEwr7/ysj4li/31wIVGggdIds9lziw7t2wr167F+QsXNO/aVaronoYESIAE/JmAaYVTKq1Zw4ZIlfIZOUSvwUPctl5SC4ijkTFBefTy1auQqDly7KotbVRrNk2qVK7K8j/5aDetNfWNV1/ViT7WQ/4XawJ8gARIwJcImFo4pduwXfNmWh8yzvndkqV6bCTzxiuvqDv379/H4WNH9dgsRiYF2Vvy9apVNYvb9JMESIAE3ErA1MIpZOpYuw/tofj6jxipM20l3Shb1tded7hy8Ii5hFNam/KtTAm8Xjk42PEePCABMxOg7yQQXwKmF05ZlmLkUHwpkidD+rRptZ7kyy564CJz585dzenOnTu6d6XhpCBX0mReJEACvkTA9MIplWH0UHwi7uLn6h9/lJ3Ltr0HD2he7ugC5qQgRUtDAiTgVgLmzNwnhFPQGzkU3zvZsomLuH7TFudVT+Jpjp08iQsXL2ouEuZOD1xopJtWsuOkIKHAjQRIgAT+IeAzwmnkUHzFA4so8YuXLuHatet6HF8zacYMzUKCpw/o1k2PXWU4KchVJJkPCZCALxLwGeGUynkoFJ+hQvG9/Zbtiy7i4y+7d8suXtut27cxc74tKEH50qUcS3LilelDD0trk5OCHgLCQxIgARJ4iIBPCadRQ/G98cqrGltXuEesXy+7eG0SyUfEUzL5uF5d2bls46Qgl6FkRiRAAj5KwKeEU+rIiKH45LuTTz+VQtzD8og1uo+rkZbghPBp+niuHG8j2xtv6LGrzLxFS1wfKchVzjEfEiABEjAAAZ8TzkdD8Y2cMMEAmIGM6TKoH8889bTu42qW/rAaJ06d0scb1Kype1ear0eP1uxSPv0M5JNgekJDAiRAAiTgIOBzwilvJqH4kiROJIcYMGIUylSvifmLl3g1JN+fl2wzYK9EfdNSnYuluXf/Pjr27K1PJUuaFEEliuuxq4xMCjpz7pxmV6syPx2mIHzP8I1IgATiScAnhVNC8dWpVg32r23tOXAAbTp3QcFywZg2dx5u374dT2yxe/zylau4ePmyPvRO9rd0HxczcvwEXL5q+y6mBFxPmDBhXLJ57DMyKQgPHujnw1p/0uSx9/ECCZAACfgzAZ8UTqnQbu3bYf/PG9HVus+cMZMk4dSZM+jYqzfylSmLIWPG4srVq5ruTnPj5i0MCgtztHa7ft4+TsVJQIKhY77RZ4NKlrS+V1s9dpXhpCBXkWQ+JBALArzVlAR8VjilNqQ786M6tbFh6SIM6dkDsphf0i9euqzC+X7J0ujarz/OnDsryS7ZJJj79p07MXTsN6hYvyGyFfoA386cpXmnTpUKz2ayibgmxMJIF+3fD/6GtDL7hHaKxZPO3SrCzM+HOceKd5EACfg3AZ8WTnvVSpCAysFBWDV3NiaPGI58eXLrJVnSMdkqagXKBKFFh07Yf+iQpsfWnDx1GuFz5uKTtu2R/YPCKpiDw8ZABFRacpKfCF6DGtXkMNbbiogIiNjLg0mTJHH5uk3JV7tprQfyx8U72W2Rjqyn/I8ESIAE/IWA0+/pF8L5MI0PPyiE2ePHYdnM6ShXooReklbiwuXLUbJqdRQKCtbu3N5DhiKmrVPvPihToxbylSpjHTsNgpwvswqcdM1KpqlTpURwqVLo1yUU239Yid+3bcFnTZvKpVhv7bt1x/2/7+tziazjmtPnzdNjVxmZFMTPh7mKJvMhARLwdQJ+J5z2Cs2WNSvCBvbHukXfo261qtoFKtdO/HEKMoFo7LdTENMmLcw9+/fj9FlbN2+iRIlQ4L330KFVSyydMR2/ronAqP59UatyZaRPl06yjvP294MHjmcvXbmCDj17q2DPXrDQJZ9Rk9amrA9NnDgxKvPzYQ7WPCABEiCB6Aj4rXDaYbz4/PPo3akjtq5cjsCCBREQkAAZrEL30gsvIKZNPhUm3a+F8ubFtyNHYPf6HzFz3Fg0b9QQ2d/MCovFYi8C8T0oGRiIBFa/AgICrPnachPBbv/VV8hRJBBtu3TD6nXr4ySi0pUskYgk14ply0BmJMsxNxIgARIggegJBESf7H+pEjhhyqgROLZjK7ZZu1Z/XLgAMW3bV6/S7tfpY8NQtFBByEQkd1Eb0qsHjoV4ancAAAWsSURBVFr9OrZjG3auXQuZVWuxiqiUd/3GTcxdtAgNW7XW8dXC5Ssgwiqics2ZjZOCnKHEe0iABEjgHwIUzn9YmOIoVcpnMHpAPxy3iujC8Kn4pH49PJf5f+r7zVu3cezESTT/sgMOHD6saU8y0k0r9/jPpCB5W24kQAIkEHcCFM64s/P6kzL7NfSzNti4dAm+nzoFhQvkV59u3rqFBi1aPVE8OSlIcdGQAAmQQKwIBMTqbt5sWALvvp0d4aNHoV/XzuqjiGLVRh9h847teNyPtDY5KehxdJjuCQIsgwTMSIDCacZai8HnWpUqOcTz8tWrqNmkKeYvWfqfJzgp6D9ImEACJEACThGgcDqFyVw3iXhWrxiiTt+7dx9tQjsjX+ky2LTtn9bnpBkz+fkwJURDAiRgI0DrLAEKp7OkTHbfwG5dsWjaVLycJYt6fjryrM68tU8aGj81XNOfTvEUZKxUT2hIgARIgASeSIDC+URE5r0hZ7ZsGmYwsFABfYkbN28ipG59LFm1ComTJNG0V19+Sfc0JEACJEACzhHwhHA65wnvcgsBiWg0ZeRIx7jnjVu38OkXHXD0+HEtL/LcOd3TkAAJkAAJOEeAwukcJ9PfJeOelYLK6XvYQ/gFWCwIiorXqxdoSIAESIAEnkiAwvlERL5zw9BePVGrciV9ocBCBfHr2jXo0r6tntOQAAmQAAk4R4DC6Rwnn7mrX5fOOPHrDkwZOQIShchnXowvQgIkQAIeIkDh9BBoFkMC0RBgEgmQgAkJUDhNWGl0mQRIgARIwHsEKJzeY8+SSYAEjESAvpCAkwQonE6C4m0kQAIkQAIkIAQonEKBGwmQAAmQgJEIGNoXCqehq4fOkQAJkAAJGI0AhdNoNUJ/SIAESIAEDE3A74TT0LVB50iABEiABAxPgMJp+CqigyRAAiRAAkYiQOE0Um34nS98YRIgARIwHwEKp/nqjB6TAAmQAAl4kQCF04vwWTQJGIkAfSEBEnCOAIXTOU68iwRIgARIgASUAIVTMdCQAAmQgJEI0BcjE6BwGrl26BsJkAAJkIDhCFA4DVcldIgESIAESMBIBB71hcL5KBGekwAJkAAJkEAMBCicMcDhJRIgARIgARJ4lACF81EinjxnWSRAAiRAAqYjQOE0XZXRYRIgARIgAW8SoHB6kz7LNhIB+kICJEACThGgcDqFiTeRAAmQAAmQgI0AhdPGgZYESMBIBOgLCRiYAIXTwJVD10iABEiABIxHgMJpvDqhRyRAAiRgJAL05RECFM5HgPCUBEiABEiABGIiQOGMiQ6vkQAJkAAJkMAjBLwqnI/4wlMSIAESIAESMDwBCqfhq4gOkgAJkAAJGIkAhdNIteFVX1g4CZAACZCAMwQonM5Q4j0kQAIkQAIkEEWAwhkFgjsSMBIB+kICJGBcAhRO49YNPSMBEiABEjAgAQqnASuFLpEACRiJAH0hgX8ToHD+mwfPSIAESIAESCBGAhTOGPHwIgmQAAmQgJEIGMEXCqcRaoE+kAAJkAAJmIYAhdM0VUVHSYAESIAEjECAwmmvBe5JgARIgARIwAkCFE4nIPEWEiABEiABErAToHDaSXBvJAL0hQRIgAQMS4DCadiqoWMkQAIkQAJGJEDhNGKt0CcSMBIB+kICJPAvAhTOf+HgCQmQAAmQAAnETIDCGTMfXiUBEiABIxGgLwYgQOE0QCXQBRIgARIgAfMQoHCap67oKQmQAAmQgAEIOITTAL7QBRIgARIgARIwPAEKp+GriA6SAAmQAAkYiQCF00i14fCFByRAAiRAAkYlQOE0as3QLxIgARIgAUMSoHAaslrolJEI0BcSIAESeJgAhfNhGjwmARIgARIggScQoHA+ARAvkwAJGIkAfSEB7xOgcHq/DugBCZAACZCAiQhQOE1UWXSVBEiABIxEwF99+T8AAAD///u+RvQAAAAGSURBVAMAhpRyy5X1kukAAAAASUVORK5CYII=</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jhaksd</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>jlkjl</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>6374532706</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>parthipancseai@gmail.com</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Madurai</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>uytuy</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>yufyf</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAc4AAAC4CAYAAABq6gzYAAAQAElEQVR4AeydB3wUVRfFz4YOKr18WLCLgqCAUoUgHRIIvXdFQJqACoQivUkvAalC6EWkFwkIiHQF6UWaQCjSmxT59t7NroghbJItM7snP+fOzJuZ9+78X+TktTsBD+5cfcCNDPg7wN8B/g7wd4C/A879DgSAPyRAAiRAAiRAAk4ToHA6jcoDN7IIEiABEiABwxOgcBq+iuggCZAACZCAkQhQOI1UG/TFSAToCwmQAAlES4DCGS0WJpIACZAACZBA9AQonNFzYSoJkICRCNAXEjAQAQqngSqDrpAACZAACRifAIXT+HVED0mABEjASAT83hcKp9//ChAACZAACZBAbAhQOGNDi/eSAAmQAAn4PQFDCaff1wYBkAAJkAAJGJ4AhdPwVUQHSYAESIAEjESAwmmk2jCUL3SGBEiABEggOgIUzuioMI0ESIAESIAEHkOAwvkYMEwmASMRoC8kQALGIUDhNE5d0BMSIAESIAETEKBwmqCS6CIJkICRCNAXfydA4fT33wC+PwmQAAmQQKwIUDhjhYs3kwAJkAAJGImAN3yhcHqDOsskARIgARIwLQEKp2mrjo6TAAmQAAl4gwCF83HUmU4CJEACJEAC0RCgcEYDhUkkQAIkQAIk8DgCFM7HkWG6kQjQFxIgARIwDAEKp2Gqgo6QAAmQAAmYgQCF0wy1RB9JwEgE6AsJ+DkBCqef/wLw9UmABEiABGJHgMIZO168mwRIgASMRIC+eIEAhdML0FkkCZAACZCAeQlQOM1bd/ScBEiABEjACwQeK5xe8IVFkgAJkAAJkIDhCVA4DV9FdJAESIAESMBIBCicRqqNx/rCCyRAAiRAAkYhQOE0Sk3QDxIgARIgAVMQoHCaopropJEI0BcSIAH/JkDhdGP9//333zh/4QL2HzqEjVu3YuHy5Rg5YSLqNGuO75Yuw4MHD9xYOrMmARIgARJwBwEKZzyprohYg3rNW+CzLl3xSdv2qNywMYqGVESOIoF4MVce5C5eEiWrVkeNjz9Biw6dMGDESKz7eRNadwpFkfIhGDc1HNev34inF3ycBPyVAN+bBDxPgMIZR+Y7dv2mIvlx23ZYu3Ej5i1ajGUREdj6yy84cuw4Ll+5+p+cU6V8BpkypEeiRAn12rGTJ9Fz0GC8W6w42nXthj0HDmg6DQmQAAmQgHEJBBjXNWN6tnvfftRu1gwh9eqrSIqXAQEByJMzJ2pXqYw2nzRB9y+/wMh+fTBjbBhWzpmF7T+sxLEd27Drx7XYsnIF9m/8CUN790LunDnkcfz111+Ys3ARylSviYr1G2g37t27d/UaDQmQAAmYhYC/+BngLy8a3/c89PvvaNK2PcrWrIX1P2/W7JIkSYKP69bBjtU/YP63k9C3cyjaNmuKhjVroHzp0iiYNy+yvvYa0qdLBxFXfchqEiVKhErlyuK7byersNaoGIJkSZNarwDbd+7Sbtz3S5VGf2u37umzkZpOQwIkQAIkYAwCFM4n1IN0p7bs0BElqlTDcmtXrNyeMGFC1K1WFT8tXoQu7doiTepUkhynTYR1QLeu2Lpqheb1/LOZNZ8/L17CqAkTkb90OZSoXBU79+zVdBoSIAESIAHvEjCHcHqB0anISHz+VXcUDamE75evgMyQTZAgAaqWD8b6xQvRu1NHZEifzmWePfP009p63WAV4/Cw0ShRpIi2UmXm7YEjR/BJu/YuK4sZkQAJkAAJxJ0AhfMRdn9evIguffujcHAFzFrwPe7fvw+LxaJdr2sWzMegHt3xbKZMjzzlulOLxYLC+fNhwrAh2LhsMfLlyaOZn7YK+eGjR/WYhgRIgARIwHsEKJxR7GUWbO8hQ5G/bBC+nTUL9sk5JQMD8cO8OTrZ58Xnn4+62zO7zBkzYeKwoUgaNf4ZNmmyZwqOuRReJQESIAG/JuD3wilrKAeNDkOBsmUx9tspuH37tv5CSKtv2czpGD90MF57+WVN84Z5KkVy1K1aRYv+bslSnD1/Xo9pSIAESIAEvEPAb4XzllUgdfJN2XIY9s04XL9xU2sgV463sWDKt5BxxmxZs2qat02TenWR0Dq+es/abSwBE7ztD8s3EAG64jQBCTwyeuIkXPjzT6ef4Y0kEB0BvxPOO3fuYHz4NGsLM0iXe1y5agtUkDNbNhVLEU0Rz+hgeSstY/r0CLG2iKX86fPmOURezrmRAAnETGDXnn0oWC5IQ132Gz4CvaxDMjE/waskEDMBvxHOe/fuIXzOXBQKKo8eXw+CTAISNLIcRLpjF02bqpNyJM2IW4uPGukkJWkZT7GOwRrRR/pEAkYiIDPhJ8+chYr16+PkqdPqWvJkSVElKEiP3WCYpZ8Q8HnhlFmxcxctQpEKIejUuw8iz53Tqn05Sxad8LNi9kzIBCBNNLARf4t+UFA9HBce7pi8pAk0JEAC/yIgITHL1qiFrv364671j2aL9WqZ4sWwaflyFMqX13rG/0gg7gR8Vjhl/ePilStRvHJVtO3SzfEX53OZ/4evu3+F1fPnQqL7WCzyv1TcAXryyWb1G2hxf168hLmLFusxDQmQwD8ETpw8hQp16yGkXn3sPXhQL3yQPy/WLlyAsV8PRKqUz2gajR8QcOMr+qRw/rBuncZ9bf5FBxw5dkzxyThhr44dsG7h96hWoTwkmIFeMJHJmzsXcrz1lnosM4DljwM9oSEBPydg75b9sFIl/PLbbqXxvwwZMebrAZgWFoaXXnhB02hIwBUEfEo4JSxdvjJl0ahVG8dfm6lTpUTntp9pSLt61atBwuW5Apy38vjUOtYpZf9+/DhWrFkjh9xMREDG2qfMmoMqDRujc5++kLXDnfv21fPwuXM14IaJXscQrj7cLXvn7l1IH1K5ksWxbtEClC1e3BA+0gnfIuAzwiljmbWbNsPpM5FaQ7L+8cuWLaxjGssgyzk00SXGu5mULloU0t0sXowcP1F23ExA4LslS1CuZm28XbgIRCi3/PILpsyeo2uHRUjlvFOvPnivZGn91Jx8hccEr+VVF0+c/APl69SNtls2bMAAyEcYvOogC/dZAj4jnPKP0NVr17SiihcpooL5aeNGjq+O6AUfMBaLBS0+aqxvsmvvXixZ9YMe0xiTwObtO1CgbDm0Du2C3/btw42bt9RR6fnIlCGDdiHKMELChAk0XdYYylpd+QpPsUpVIOsOz5w7q9do/iEwf8lSfGjl8+vuPZrIblnFQOMhAj4hnBcvXcbAkSMVmazHnDhsCCRouib4oKkaHOz4a3rAiBE++IbOv5KR79x36CCkF+SP02fUTYvFgnLWrsPvp07B79u2YMvK5fhx4QIdRji8ZTNmjA1DFWvdpkieTO+XT9nJukP5Qk6NJk0xZ+Eih/DqDX5ozl+4gAatWqFNaGfcuXtHu2XLFCvKblk//F3w5iv7hHD2HDxYgwJYLBYM+KqLN3l6pGz5nue7b2fXsv5+oDsagxHYvH07KtRpYP3H3TbmFlyqJHauXYOwrwfAXncPuyzfa5Xvtw7u2R2/RKyG7IsUyK9fyJGJLxu3bEG7rt2QM/BDlK5WXT9AYA8P+XA+vnxsb2VGrNugr/nKi1mwePo0jB00yPGHpF6gIQE3EzC9cG779VfMi1qaUb96Nbz52utuRgaMGD8BVRt/hInTZri9rMcVkDdXLr106/Yt3dMYi0CjNm1x+y9b3OOhfXpjVP9+Ti+FkKD+0vKcOnoUtv+wEl3bt4M9/OOdO39h78FD+sm7bB8U0dbXVOtYqXTxep+A6z2QyVQLl61AYEhFbWVKpC+LxYLmjRpi5ZzZePutN11fKHMkgScQMLVwyoSg0N799BXTpE6FL1q21GN3m6lz5kLGrkZOnODuoh6bv4yPycXzF/4El6UICeNsyyMicC1qvL16hQqoWLZMnJ1LmyYNPqpTG/LBgYjv5iGoZAkkSpgI8iNf8JHWV2ifvshVrASCatXB4LAxkLFvuW7WTcRy9br1uv46R5FAtOjYEb8fO66vI4FAFoZPQYdWLSE9L5pIQwIeJmBq4ZTZiDKOJMxCP/sMMpNWjt29PZspoxZx6fIVSOB1PfGwsQuniGbk+XMeLp3FxURgwIhRejl1qpTo1amDHrvCvPrSSxg9oD+ObNuMNQvmI/SzNng/17vanSv5i2AOHfuNCug7RT+EBAKYv3SJKZa4iFhGWLtgW3cKhYhlw1atIRG/JMSkvFuAtZUZXKoUVs2dDZnHIGncYibAq+4jYFrh1AlBo/6ZEFS1fLD7KD2Sc0trN60kSYt3527bYms59+QmMzHt5UWe5afG7Cy8vV9mbW0ePnpU3WjRuLHbxt5eefFFfFK/HuZaez1++3Ethvfto5Gw7JPi5P8PCQTQplMXwy5xsYtl2y7d8E7RYtrt/N3SZTpfQQDKsit5R4kjfeyX7dbu7r5sZQoYbl4nYFrh9OaEoLx5cjv+yo9Yb5uo4OmazJQhvaNItjgdKLx+MPCh1ma9alU94s/TTz+FkDKlMbJfH/y6NgIzvxmDUkWLIkGCAC1fxj+NsMRFekckcId8pKBczVq6plVmyErL0r6UTHpSmjaoh4XhU7HR2lqWVjVbmFqNNAYiYPs/KzYOGeDenXv2eHxC0MOvLcsFUj3zjCbNW7xE9542MvaVMEECLTby7Dnd03iXgKdamzG9pfxOFHj/fYwbMghHtm7x2hIXu0guWLZcoyNV++hjZCv0AQIrVETnvv3x2779jqU1D7csZYlOpzZt8E72bDG9Jq+RgFcJmE44pXv0i696KjRPTgjSAh8y7+fOpWenIyNx7ORJPfaksVgssHfX2r/44snyWdZ/CXijtflfL/5JCQgIQMG8eXVpS8xLXIpCgi106NlbRU7CAMZlkxCC5evUQ1DtOg6RbNWxEySu8qZt2x1dsAkCAiATnEoEFoGsaWXLEvwxGQHTCae3JgQ9Wq99OnWE/HUv6ZNnzpSdx7dMGTNomWejPpWmJzReIWCE1mZMLx7zEpc7kGAL0+fNU5EToYvLJtG7frWO+e/as9chkjLzVZaM1K5SGf26dsbSGdNxaMsmneA0YeiQaNe0xvQevEYCRiBgKuGUCQ8DvTQh6NHKSpc2LYJLldTk2d8vxK3btjV7muAhkzF9Bi0p8hwnBykILxqjtTZjQiHd/A8vcSlSoIC2ADNnzKghAF964YU47dOnTYNkSZIiX57c6NclFIunh+PAzz9hyfRp6Ns5FLUqVUL2N7Oa/kMLMbHlNf8gYCrh9OaEoOh+HZrUr6fJ16/f0EgueuJBkymjbYJQJFucHqT+36Imz5oFnUlrveTOmbTW7F3+nyxxmTp6pLYAN61YpiEAJQxgXLbtq3/Agc0bMXv8ONSqXFk/gScxeV3uNDMkAS8TMI1wLlyx3KsTgqKrp2xvvOHoaho/NdzjgQgypc+obp05e1b3NNETkMg6EjS93qctULJqNSxZtSr6G+OQKuPbvb4erE8mTpwInppJ75mKYwAAEABJREFUqwXSkAAJeIWAaYSzz+BhCihxokTwVIQgLfAJpkHNmnrHiVOn8P2yFXrsKZMpYwYtSrqJr127rsc0NgIz5i/QCS/yGS+JrLN7336s/Wkj9h86rBFpDhw+bLsxHlaGDuo2+1Tj0Uo2DWrUcNu6TcmfW6wI8GYScBsB0whnWuuYolB4643XPRYhSMp70hZcsgSSJE2it/UbPlz3njKZ0tu6aqU8ruUUClBxLFuzNr7s0UMnvFy5ek0vyESu5CmS67H8odGgRSvERzwlwHqj1q1x/I8/NE+Jndq57Wd6TEMCJODbBALM8noZ06VTV9OlSat7oxgZwymQ5z1159yFC/BkCD57i1MKj2T0IKzZ8BNEzHbv2ydIYAmw4P1338X0MWH4fftW7P9pg87slIunIiMRUrd+nLpt5WslrTp1xo5dv0lWCC5VSmOn6gkNCZDAfwn4WIpphNPI3OtXq6buSQixnbv36LEnzHOZMzuK8ecWp/yx0nfYMNRv0RL37t0HLBZUKR+MPevXY+6kCSiULy/sPzKzU5ZFyPmNW7fQJrRLrFuePQYNggRylzzy5s6FYb17yiE3EiABPyFA4XRBRUsIPovFojlt2rZN954w0v2YMiqCUaSfThDad+AgAiuEIGzSt4o8d84c2LxiKQb36P7YLn0Rz0pB5fT+v+7cQdVGH2Hzju1w5mdC+HTH5+QkXuwkq2BLr4Mzz/IeEiAB3yBgcuE0RiVICL6337R9F/BnDwqnvH3a1Glkh8PHjunen8y6nzchuE5dnPjjlL52s4b1MWfiBPwvg222sSY+xgzt1dPRbXv56lXUbNIU85csfczdtmRpZcqSKDmTdbwzvhmDp55KIafcSIAE/IgAhdNFlZ3/vTya06btOyBdh3riAXPj1g0tZfuvO3XvD0b49h02HHWaNdcZrRaLBR1at0TH1q0d0Zyc4SAtz+oVQ/RW6eJtE9oZ+cuWw7qNmzRNjD3m6qiJE9H8iy8h45vJkyVFeNgoSEByuYcbCZCAfxGgcLqovvPntgnnHWvXnyfHOdOmSq1vkCljRt1703ii7HPnL6BC3XrWrtnJWpyEc9u6cgWaN2yo57E1A7t1hXy26uUsWfTRU6fPoE7z5igaUglla9ZyxFztP3wkRFwtFgvCBg7EW6+/rvfTkAAJ+B8BCqeL6txr45wJE+obvJzlBd37spGu2WKVq+C3vftgsVggn5+SIOEZ0ttmXMf13eWzVavmzkahfPkA21A1jhw7Bln7ef3GTchPggQJkCRxYjSqVRNFCxUEf0iABPyXAIXTRXXvrXHOGzdt/7AnT57MRW9ivGyka7bP0KGo2/xTXLGOR8qEqKmjR0E+PyUTpFzhsQQjnz5mNPZu2IBSHwZChPK9d991xFw9tPlnDU7e7fP2rijOA3mwCBIgAXcRoHC6kKw3xjlv3rylb5AiuW9OUrF3zY6ZPEVDGkrX7Op5c1E4v7V1qG/uWvNUiuQYN3gwjm7finmTJjDmqmvxMjcS8AkCFE4XVqM3xjlv3LK1OFMk870Wp7u6Zl1Y5cyKBJwiwJt8iwCF04X1KeOciBokm7twITzxc/2GbVZtCmtLyRPleaIMT3TNeuI9WAYJkIBvEqBwurBeZZzz6aeSa44RG37SvTvNX3/9BVkeIWWkSG4rV47NvO09cACB5UNg75rNleNtrJw7y21ds2ZmRd9JgATiQiD+z1A448/wXznkj4pbe+HiRYeo/esGF57ciBrflCyT+4Bwbti0GeXr1IN8aUbeqVnDBpg7aaJTAQ3kfm4kQAIk4AkCFE4XU27aoJ7mePfuXcgYnZ64ydy8ZZsYJNmnSGbeFqcEGRj2zTjUatrMEdDgy5afomPrVrEKaCAcuJEACZCAuwlQOF1HWHPK8847SJvGFpRg3c8/a5q7zI2btvFNyT+FSZejXLt2HbWbNceg0WHyGsj62mvYuGwJPm3cWM9pSIAESMBoBEwjnPbW1R1rS85oEB/1p7AspLcmurvFaV+cby0KZpwctP/QIZSsWg3SRSvvEFKmNBZPm4pnM2WSU24kQAIkYEgCphFOieQiBHfs2uX2sUMpJz5b4fz59fGDR47g6IkTeuwOY1/DKXmnMNk6zgXLliOodl3IdzETJ06Mvp1DMbxvH8ixvE+8N2ZAAiRAAm4iYBrhLPDee4pAll8sWLpMj41qCj+0ON+d3bX2AO/CwZPrOJesWoUi5UPwQVB53cu5+ODMJmO/HXr0QquOnSBxfSVQ+vdTJqN2lcrOPM57SIAESMDrBEwjnIN7dsdzmf+nwPoNH4F79+7psRFN+nTpIMsoxLeHv7Qh567cHm5xJvfQrNoVERFo2TFUW9LH//hD9y2tIvi4P2YuXb6CvQcPYs2GnzBm0mTkLxuE6fPnK4aCefNixexZyJY1q57T+CwBvhgJ+BQB0winxA7t3K6two88dw7jw6frsVFN4aju2nWbNrmta/lGVJxaYZAsaVLZuX1r1627448WS4Dt1+fevfto1SkUxStXQ4OWrVCjSVNtib6erwByBhZF6Wo1UL9FS/QZNhznzp9XH1s1+QjTwkYhdaqUek5DAiRAAmYhYPuXzyTeli1WDNnftLVOho8fh+vX/5lVarRXKBzVXStBCtw1Scg+OUjiq3ri/Q8cPoybt21LYJInS4bjO7YhuHQpR9EHjxxGxPoN2Lhli7ZEb9++7bgmwdhTpUwJCabe5pMmaN+8OQKihNdxEw9IgATcT4AlxJuAqYRT3rZnhy9lp6I59Jtv9NiIJo8HlqXctMep9cDEoM3bd6Byw8a4d9fWRV662IeKfVS/vtj70wZUKR+MBAkTIMdbb6FZw/r46vPPMXbw11gYPhVbV63AkW1bsOvHNTiydTPaNmuqz9KQAAmQgBkJmE44c+fMiZKBgcp64vQZkG5bPTGgcfeyFHtXbQoPjG82adcOV69dU8r9unbG0F499ViMtHgH9+iOo9u2YvH0cHRs3RqNatdEmQ8/xDvZsyFj+vSwWKI+dCkPcCMBEiABExNwoXB6jkKnz1ojQYIEuHfvHvoOHea5gmNZUuGocc6DblqWYp8clNzNwQ9kycilK1f07UPKlkGtSpX0mIYESIAE/JGAKYXz5SxZUD0kROvru6XLIGNvemIwUzhqnFPcWrRypexcup05e1bzC3Bza276vPnAA+gay35dumiZNCRAAiTgrwRMKZxSWZ9/2gxJkiSRQ3TrP1D3RjOyLCVNalv4vWlz5rncvf2HD2uekedsM1X1JMq4aidfX5n53QLNrqK1tZk8mWdm72qBNCRAAiRgQAKmFc60adKgaf16inTj1q34caN748JqQXEwr7/ysj4li/31wIVGggdIds9lziw7t2wr167F+QsXNO/aVaronoYESIAE/JmAaYVTKq1Zw4ZIlfIZOUSvwUPctl5SC4ijkTFBefTy1auQqDly7KotbVRrNk2qVK7K8j/5aDetNfWNV1/ViT7WQ/4XawJ8gARIwJcImFo4pduwXfNmWh8yzvndkqV6bCTzxiuvqDv379/H4WNH9dgsRiYF2Vvy9apVNYvb9JMESIAE3ErA1MIpZOpYuw/tofj6jxipM20l3Shb1tded7hy8Ii5hFNam/KtTAm8Xjk42PEePCABMxOg7yQQXwKmF05ZlmLkUHwpkidD+rRptZ7kyy564CJz585dzenOnTu6d6XhpCBX0mReJEACvkTA9MIplWH0UHwi7uLn6h9/lJ3Ltr0HD2he7ugC5qQgRUtDAiTgVgLmzNwnhFPQGzkU3zvZsomLuH7TFudVT+Jpjp08iQsXL2ouEuZOD1xopJtWsuOkIKHAjQRIgAT+IeAzwmnkUHzFA4so8YuXLuHatet6HF8zacYMzUKCpw/o1k2PXWU4KchVJJkPCZCALxLwGeGUynkoFJ+hQvG9/Zbtiy7i4y+7d8suXtut27cxc74tKEH50qUcS3LilelDD0trk5OCHgLCQxIgARJ4iIBPCadRQ/G98cqrGltXuEesXy+7eG0SyUfEUzL5uF5d2bls46Qgl6FkRiRAAj5KwKeEU+rIiKH45LuTTz+VQtzD8og1uo+rkZbghPBp+niuHG8j2xtv6LGrzLxFS1wfKchVzjEfEiABEjAAAZ8TzkdD8Y2cMMEAmIGM6TKoH8889bTu42qW/rAaJ06d0scb1Kype1ear0eP1uxSPv0M5JNgekJDAiRAAiTgIOBzwilvJqH4kiROJIcYMGIUylSvifmLl3g1JN+fl2wzYK9EfdNSnYuluXf/Pjr27K1PJUuaFEEliuuxq4xMCjpz7pxmV6syPx2mIHzP8I1IgATiScAnhVNC8dWpVg32r23tOXAAbTp3QcFywZg2dx5u374dT2yxe/zylau4ePmyPvRO9rd0HxczcvwEXL5q+y6mBFxPmDBhXLJ57DMyKQgPHujnw1p/0uSx9/ECCZAACfgzAZ8UTqnQbu3bYf/PG9HVus+cMZMk4dSZM+jYqzfylSmLIWPG4srVq5ruTnPj5i0MCgtztHa7ft4+TsVJQIKhY77RZ4NKlrS+V1s9dpXhpCBXkWQ+JBALArzVlAR8VjilNqQ786M6tbFh6SIM6dkDsphf0i9euqzC+X7J0ujarz/OnDsryS7ZJJj79p07MXTsN6hYvyGyFfoA386cpXmnTpUKz2ayibgmxMJIF+3fD/6GtDL7hHaKxZPO3SrCzM+HOceKd5EACfg3AZ8WTnvVSpCAysFBWDV3NiaPGI58eXLrJVnSMdkqagXKBKFFh07Yf+iQpsfWnDx1GuFz5uKTtu2R/YPCKpiDw8ZABFRacpKfCF6DGtXkMNbbiogIiNjLg0mTJHH5uk3JV7tprQfyx8U72W2Rjqyn/I8ESIAE/IWA0+/pF8L5MI0PPyiE2ePHYdnM6ShXooReklbiwuXLUbJqdRQKCtbu3N5DhiKmrVPvPihToxbylSpjHTsNgpwvswqcdM1KpqlTpURwqVLo1yUU239Yid+3bcFnTZvKpVhv7bt1x/2/7+tziazjmtPnzdNjVxmZFMTPh7mKJvMhARLwdQJ+J5z2Cs2WNSvCBvbHukXfo261qtoFKtdO/HEKMoFo7LdTENMmLcw9+/fj9FlbN2+iRIlQ4L330KFVSyydMR2/ronAqP59UatyZaRPl06yjvP294MHjmcvXbmCDj17q2DPXrDQJZ9Rk9amrA9NnDgxKvPzYQ7WPCABEiCB6Aj4rXDaYbz4/PPo3akjtq5cjsCCBREQkAAZrEL30gsvIKZNPhUm3a+F8ubFtyNHYPf6HzFz3Fg0b9QQ2d/MCovFYi8C8T0oGRiIBFa/AgICrPnachPBbv/VV8hRJBBtu3TD6nXr4ySi0pUskYgk14ply0BmJMsxNxIgARIggegJBESf7H+pEjhhyqgROLZjK7ZZu1Z/XLgAMW3bV6/S7tfpY8NQtFBByEQkd1Eb0qsHjoV4ancAAAWsSURBVFr9OrZjG3auXQuZVWuxiqiUd/3GTcxdtAgNW7XW8dXC5Ssgwiqics2ZjZOCnKHEe0iABEjgHwIUzn9YmOIoVcpnMHpAPxy3iujC8Kn4pH49PJf5f+r7zVu3cezESTT/sgMOHD6saU8y0k0r9/jPpCB5W24kQAIkEHcCFM64s/P6kzL7NfSzNti4dAm+nzoFhQvkV59u3rqFBi1aPVE8OSlIcdGQAAmQQKwIBMTqbt5sWALvvp0d4aNHoV/XzuqjiGLVRh9h847teNyPtDY5KehxdJjuCQIsgwTMSIDCacZai8HnWpUqOcTz8tWrqNmkKeYvWfqfJzgp6D9ImEACJEACThGgcDqFyVw3iXhWrxiiTt+7dx9tQjsjX+ky2LTtn9bnpBkz+fkwJURDAiRgI0DrLAEKp7OkTHbfwG5dsWjaVLycJYt6fjryrM68tU8aGj81XNOfTvEUZKxUT2hIgARIgASeSIDC+URE5r0hZ7ZsGmYwsFABfYkbN28ipG59LFm1ComTJNG0V19+Sfc0JEACJEACzhHwhHA65wnvcgsBiWg0ZeRIx7jnjVu38OkXHXD0+HEtL/LcOd3TkAAJkAAJOEeAwukcJ9PfJeOelYLK6XvYQ/gFWCwIiorXqxdoSIAESIAEnkiAwvlERL5zw9BePVGrciV9ocBCBfHr2jXo0r6tntOQAAmQAAk4R4DC6Rwnn7mrX5fOOPHrDkwZOQIShchnXowvQgIkQAIeIkDh9BBoFkMC0RBgEgmQgAkJUDhNWGl0mQRIgARIwHsEKJzeY8+SSYAEjESAvpCAkwQonE6C4m0kQAIkQAIkIAQonEKBGwmQAAmQgJEIGNoXCqehq4fOkQAJkAAJGI0AhdNoNUJ/SIAESIAEDE3A74TT0LVB50iABEiABAxPgMJp+CqigyRAAiRAAkYiQOE0Um34nS98YRIgARIwHwEKp/nqjB6TAAmQAAl4kQCF04vwWTQJGIkAfSEBEnCOAIXTOU68iwRIgARIgASUAIVTMdCQAAmQgJEI0BcjE6BwGrl26BsJkAAJkIDhCFA4DVcldIgESIAESMBIBB71hcL5KBGekwAJkAAJkEAMBCicMcDhJRIgARIgARJ4lACF81EinjxnWSRAAiRAAqYjQOE0XZXRYRIgARIgAW8SoHB6kz7LNhIB+kICJEACThGgcDqFiTeRAAmQAAmQgI0AhdPGgZYESMBIBOgLCRiYAIXTwJVD10iABEiABIxHgMJpvDqhRyRAAiRgJAL05RECFM5HgPCUBEiABEiABGIiQOGMiQ6vkQAJkAAJkMAjBLwqnI/4wlMSIAESIAESMDwBCqfhq4gOkgAJkAAJGIkAhdNIteFVX1g4CZAACZCAMwQonM5Q4j0kQAIkQAIkEEWAwhkFgjsSMBIB+kICJGBcAhRO49YNPSMBEiABEjAgAQqnASuFLpEACRiJAH0hgX8ToHD+mwfPSIAESIAESCBGAhTOGPHwIgmQAAmQgJEIGMEXCqcRaoE+kAAJkAAJmIYAhdM0VUVHSYAESIAEjECAwmmvBe5JgARIgARIwAkCFE4nIPEWEiABEiABErAToHDaSXBvJAL0hQRIgAQMS4DCadiqoWMkQAIkQAJGJEDhNGKt0CcSMBIB+kICJPAvAhTOf+HgCQmQAAmQAAnETIDCGTMfXiUBEiABIxGgLwYgQOE0QCXQBRIgARIgAfMQoHCap67oKQmQAAmQgAEIOITTAL7QBRIgARIgARIwPAEKp+GriA6SAAmQAAkYiQCF00i14fCFByRAAiRAAkYlQOE0as3QLxIgARIgAUMSoHAaslrolJEI0BcSIAESeJgAhfNhGjwmARIgARIggScQoHA+ARAvkwAJGIkAfSEB7xOgcHq/DugBCZAACZCAiQhQOE1UWXSVBEiABIxEwF99+T8AAAD///u+RvQAAAAGSURBVAMAhpRyy5X1kukAAAAASUVORK5CYII=</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>cdevfrgb</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>dcefvrgbt</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAdQAAAC2CAYAAABgbHyJAAAQAElEQVR4AeydB3xURdfGnxBeBSkqIl3AivTeCZBA6L0GCIFQBaX33nvv0kEgEHpJ6CRAaJEaOioIfiio9P5Svz0n2X1REAnJZu/effJj5s7OvXfKfy57du6Zcybes4e3njGQAZ8BPgN8BvgM8BmI2TMQD/wjARIgARIgARKIMQEK1BgjfEUBPEUCJEACJOAyBChQXWao2VESIAESIAF7EqBAtSddlm1PAiybBEiABAxFgALVUMPBxpAACZAACTgrAQpUZx05tpsE7EmAZZMACUSbAAVqtJHxBhIgARIgARJ4kQAF6otMmEMCJEAC9iTAsk1KgALVpAPLbpEACZAACcQtAQrUuOXN2kiABEiABOxJwIFlU6A6ED6rJgESIAESMA8BClTzjCV7QgIkQAIk4EACLiBQHUiXVZMACZAACbgMAQpUlxlqdpQESIAESMCeBChQ7UnXBcpmF0mABEiABCIJUKBGcmBMAiRAAiRAAjEiQIEaI3y8mQTsSYBlkwAJOBMBClRnGi22lQRIgARIwLAEKFANOzRsGAmQgD0JsGwSiG0CFKixTZTlkQAJkAAJuCQBClSXHHZ2mgRIgATsScA1y6ZAdc1xZ69JgARIgARimQAFaiwDZXEkQAIkQAKuSSCuBKpr0mWvSYAESIAEXIYABarLDDU7SgIkQAIkYE8CFKj2pBtXZbMeEiABEiABhxOgQHX4ELABJEACJEACZiBAgWqGUWQf7EmAZZMACZDAaxGgQH0tTLyIBEiABEiABF5NgAL11Xx4lgRIwJ4EWDYJmIgABaqJBpNdIQESIAEScBwBClTHsWfNJEACJGBPAiw7jglQoMYxcFZHAiRAAiRgTgIUqOYcV/aKBEiABOxK4LfLf6B20+bo0n8g7t27Z9e6DFn4SxpFgfoSKMwiARIgARJ4kcCDBw9w8swPaNerN4qUL4/wgwcRuHo1vGvVefFiF8yhQHXBQWeXSYAESOBlBG7euoURkyZhzqIATJgxE90HDkajb9qowMzmUQJfFCqCcnV9sCp4PZ4+e2YrIl2a1La0KycoUGNt9FkQCZAACTgfgUt//I65AUvg0+Ir5CjphSmz56L/qNEYM3UaAlauROiu3Tjz00+4dfv2XzonQnTyiOE4FBqCwFkz/3LOVT9QoLrqyLPfJEACLkvg9I8/YuKMWahQrz4KlimPfiNHYs/33+PZ06fKJFGiRMiVLSvKenrCv54PerRrh4nDhmLF3NnYHRyEcwf3Y8/6YFQpWwbJ339P72EEUKDyKXAKAmwkCZDAmxN4ahGU+w8fxuCx4+BRqQrK1K6L0VOn4vip01pofHd3FC1YEAO7d0P45g04tTsMaxcuwMxxYzCgW1e08m+EauXLIX/u3PgobRrI9Xojo78QoED9Cw5+IAESIAFzEHj48CG27QxD1wEDkbe0N2r6N8WM7xbgwsWL2sF3EiZAhVKlMH7IYERsD8Xi6dPQ2KcuUqdIqecZRZ8ABWr0mfEOEjAZAXbHLASuX79hEaCD4N+mHbIXLwn/tu2wZNVqXL12Xbv4/nvvom61qpg3cSKO7tiOb8eMQo2KFZAkSWI9zyhmBChQY8aPd5MACZCAwwls2bEDbbr3QE5PL4sAXYVtYWG4/+CBtit92rRo2chP9Z+HQ7ZhVP9+8CpeDG+99ZaeZxR7BChQY48lSyIBEiCBFwjYK+PoyZMYOHqMzkSbtuuANRs32apKkzIVOrdujU3LlmBX8Dr06tBe9Z/x4vEr3wbJDgnStQNUFkkCJEAC9iDw55UrmDZ3HkrVqIVK9X0xa+EiiO2o1JU2dWq0ad4MO9etwb5N69G2RTNk/vwLOcUQRwQoUOMINKshARIggTchcO/+A6xYF4R6LVshf5lyGDZhIn48d06LSpzoHdSpWgWBs2Zgz/ogdPm6NTJ+9JGec43IWL2kQDXWeLA1JEACJAAxc9m1Lxzte/dBHi8vdOjTF7vDwzXf3d0dJYsWwaThwyA60dED+qNwvnxwc3MjOQcToEB18ACwehIgARKwEjh34YLOQAuVq4D6X7XCyqBgyAxVzsvr294dO+DAlk34bspkVC1XFm+//bacYjAIAbMJVINgZTNIgARI4PUI3Lh5C3MWLVavRSWrVlcd6eU//tCbP0yeHM0b+mLj0iW6wKiFX0N8kCwZ+GdMAhSoxhwXtooESMDEBMTpQvCWLWonmserFPqPGmXzWpQgQQKdfcosdP/mjejTqSOyfPGFiWmYp2sUqOYZS/v3hDWQAAnEiMCBI0fQfdAQ5CnljVZdukE8GT1+8kT1n4Xy5YXYiIpeVPSjoielmUuMcMf5zRSocY6cFZIACbgSgV8vXcK4b6ejWMXKqNG4CQJWrLDt3PJJhgxqL7p3YzCWzpqpXowSvZPQlfCYqq8UqKYaTnbGiQmw6SYi8OjRI3VELwK0cPmKKlB/+fVX7WHSJElQv0YNrJo/F9vXrFJ7UXHEoCcZOTUBClSnHj42ngRIwEgEfr18Gf1HjsKn+QuqI3p5xWttX5mSJTF97GgcD9uB4X17I2/OnNZTPJqEgNMI1Os3bqFz/wGYH7gUq9ZveO3wneX6LgMG4Mq1qyYZMnaDBEgg2gTsfMOR4yfQumt3FC5XAXMCFttqy5AuLYb36YVjO7dj1vixKO/lZTvHhPkIGF6g3rl7T1+X5CtdGktXr0GfYcPRrmev1w69LdcHrlqDvKXKoO/wEfjh7FnzjSJ7RAIk4BAC4pS+dtNmqOLbEEGbN9vaIHuHLpg6BWFB61C/Zk28mzSp7RwT5iVgWIF6/peL8PumDfKXKasC9dHjx4jJ37NnzzBvSSBK16yNlh07I2xveEyK470kQAIuTEAWFonNaNN2HRB+8JCSSJI4MZrUr4fggEWYOGwoShQprPkuELGLUQQMKVDv3b+Pqg0bYvuu3bh79642taK3N5bMnInTe/dEO6z6bj58a9fSciTaEBKCBq1aoXqjxli+bp1kMZAACZDAKwnIdmjjp8/Q3V3E9EW8GskNGdKlQ8dWX2HT0iXo37ULsmfJLNkMLkjAcAJVdk6oXN8X12/e1OH47JNPsNoiEKeNGoEi+fPinYQJoh3y5siOob164nDIVn3wU374oZZ9MOIoOvbphyLlK2LK7Dm2XRv0JCMSIAESsBCQ1bm9hg5DpkJFMHbat7bvidzZs2Fwz+7YuDQQ7Vu2QLo0aSxX858rE7CLQI0J0DK16+LHn3/WIvx86iBk5XLksQhEzYhhJC675MHfv2UTRvTtgxxZsmiJFy9dwohJk5HbqzT1rEqEEQmQwMGICLTo2EntRxcsXWYD4uVRDFNGDMOaBd/Br04d0G7UhsblE4YTqLfv3NFBSfTOOxjcvbum7RHVq1EdQQELMW/SRHiXKKFVPLboaalnVRSMSMBlCWzYFoLqjf0tKiF/bAwJtXGoWbkSFk+fBvnOqFy2rC2fCRKwEjCcQM2e+UttW4440kPIr83ZE8ZhQ+BiJ9GzKh5GJEACsUxATOw8q9VAy06dcfBIhJYus89mvg30+2HcoIEoWrAg+EcC/0TAcAI1cNZMHAoNgRz/qdH2yM+aKdMr9ayynVKrLl1w+fc/7FE9yyQBEnAAgTt37mLM1GnI5emF3sOG4+z589qK9GnTous3XyNk9Ur07dwJWS3fD3qCEQm8goDhBKq0Nfn778nBIeGf9Ky/Xb6M4C3b4FWzJu7eu++QtrFS+xNgDa5BQFbodhs4GNmKl8CEGTNx7foN7bis1xjWuxe2rliGb5o1ReoUKTWfEQm8DgFDCtTXaXhcXPO8nvXzTz7VKuUXrd/X30CW0GsGIxIgAachIDajzdp3hNiQLl65Ek+fPtW2ly5eHN+OGaUWBQ1q1YRsoaYnGJFANAhQoL4GLNGzblkeCO+SkYuX9h8+jKbtO0AcYL/G7byEBEhACTguCtq8GTX9m0C8Gm3evt3WkDpVq1jUSzMwZ+J4VChVypbPBAm8CQEK1NekJvsSzhgzGiJc5ZZd+8LRvGMnPHnyRD4ykAAJGJDA3IAlKFWjFlp37Y79h49oC9966y20bOSHLcuXYvSA/iicL5/mMyKBmBKgQI0GQXd3d8wcOwbFCkWu9AsJ24W2PXvbXhtFoyheSgIkYCcCN27eUrvyvKXLoN/Ikfjx3DmtKW2qVOjRri32BAehV4f2yPTZZ5pvloj9cDwBCtRojsF//vMfzJ0w3uZsYt2mTejYtx/EVzD4RwIk4DACIji7DRiEvKW91fPZn1euaFtyZMmijlzCgtailX9jpPgwueYzIoHYJkCB+gZE3377bSz69lubz86VQcHoMWjIG5TEW0iABGJKYM/330M2vJBXu4tXrbKtbfAqXgwzx41RBy6ywDB+/PgxrYr3uyyB1+s4BerrcXrhKjH4XjJ9OjJ//oWeC1i5EkPGjdc0IxIgAfsTWL1hI+o2awGfFl9hQ0iIrUJZaLR8zmzMmzgRZT09bflMkIC9CVCgxoBwkiSJdYXgx+nTaynT53+HSTNnaZoRCZCAfQjMXLAQ4vO7bY+e2HvggFbiHs8drZv4I2TVCl1oVCBPbs1nRAJxSYAC9c1o2+56792kWDZ7Fj5Km0bzRk2ZCvEHrB8MGF25eh3SxmOnThmwdWwSCbycwNVr1zBy8hQUKFMOg8aMxekff9QLZecoWWC0f+smdG/bBp99/LHmMyIBRxCgQI0F6rLIYdmcWbbFDn2Hj4DoVWOh6BgX8d///hc79+7DsAkTUd6nPvKUKqWz6Ir1GiBLMQ+1y+s9bDgWLluOA0eO0AtUjImzgNgkcMoiOHsOGYrCFSph8qzZuPxHpOvPrJkyYczAAQjftEFNYJInSxab1bIsEngjAhSob4TtxZvSpEylM9UPkr2vJ2Xlr6wA1g9xHB05fgJT58yFT/OW+LxgYfi2ao1pc+fhxOnTf2mJeH0SzzHiFFy+tGo0boLMRYqicPmKaNK2vZoerNm4CSd/+CFu7W3/0kp+cEUC8iOwVZduKFu7rv7Ye/DggWIoUaSwOmHYELgYtatUhtiH6wlGJGAAAhSosTgIokuV17+iWxWXZmKjKraqsVjFS4v6+ZdfIPs1ykrH7MVLoopvQwyfOAl79u+3XZ82dWr4VK+GycOH4vtNG7H6u/lqSuBfzwdFChRA0iRJbNf+eukStu7cqaYHbbr3QLk6Pvi8QCGd4bbr2Qvjv52O/iNH4fqNm7Z7mCCB2CAgb3bqtWylPwKDt2yxFVmjUkWsnj8PC6ZOgbgJtJ1gggQMRIACNZYHQ3Q4S6ZP102HxYuSeFMSr0qxWc3Va9chKxw79+uPwuUqoESVaug1dJiudLx565ZWJbpdcaU2tFdP7Fy3Bns3BGNkv76oUq4cUqVMoXa0YkowoFtXLJnxLY6H7cCBLZsR8O00NXqXvR+zfvklxKuMFPj4yROcsMxwV63fgLEWgTonYDHylylrmfnOt5kpyHUMxZMSDQAAEABJREFUhidguAbK/5M5ixbrD7b2vftgd3i4rY0t/Bpi+5pVGD94EPLkzGHLZ4IEjEiAAtUOo5I9S2a1UxV7VfH369+uPQ4dPfbGNd27/wAy0x04eoyubsxTqjRkhePSNWvx6+XLWq7UJR6cxBNMUMBCHAkNgTj79q1dCxk/+kiv+bdIdMFSRstGfpC9HzcsCcAP+/YgdPVKzBg7Gu1aNNfZwbtJkmpRDx8+tOhmJ6B45aqQmQWdWygWRq9JQPShsnWaR6Uq6D9qlP5gk1tFH9qzfXsc3bEdvTt2wCcZMkg2AwkYngAFqp2GKE+O7BCPSuJZSRYGNfjqKxw7+Xora+UX+8GICIyfPgO1mjRFNo/iaNymLWYtXKSrG0Vwie5IPMCIqcDi6dNwwjLDlNmleIKRfDkfG12Tcj7NmBHlvLzQqXUr1V8dC9uuwjpjlKAWoS4ziwo+9XH42PHYqJZlmJiA/D/oM2wEPKtV163TLlpUDNJdcQU4dtAAHArZiq8a+0Heski+UwU21qUJUKDacfhltie+f93d3XX1rE/Lljj14w8vrfGHs2chr72atG2P7MVLoHojf4yd9i2+P3QYjx8/1ntEgMmM89sxoyy/3kPVA4yYChQtWND2alYvjIOoQqlSavPXv0sX2xffiTNnULWhH5p36IQLFy/GQStYhTMR2L57D0QnX7F+A8wPDNT/E9J+0eHPnzxJndXXqlxZshhIwCkJUKDaedi8PIph4tDBuhrx9u076tlFFhH9eeUKlq9bh/a9eiOfdxmUrllbX3vJYqA7d+9pqz5Ilgyi8xTdZ/jmDaoLFZ2oCLOkzy0i0osdEIkrtyYN6mFX0Dr41/eBfJZmbAoNhew3Wad5C1z6PdLMQfIZXJOA6Psbtv4aso/wmo2bbBCqliuLtQsXqA7fs1hRWz4TJPAPBAyfTYEaB0NUuWxZiCB0c3OD7IThVb0m8pYug459+mFl8Hr88ecVbcU7CRNAvlj6dOqITcuW4NC2LboqV1bnpk6RUq8xYiTCfUDXrtgVvFZ/AEgb5bX1vv0H1M5VPjO4FgHRr4uDk0r1fVXfv2PPXhsA/REWvA6Thg9DrmxZbflMkICzE6BAtdMIymKkfQcOYvTUqajm10hX4YruU6oTYSPH+O7xkDdnDl3sI+Y2x8N2Ql59NW/oqz6C3dzc5DKnCWlSptIfALIoyuo56hfLq9+z5887TR/Y0JgREH2o6P7lR6M4ODl68qQW+G7SpOjW5huLrn8nRE2QPm1azWdEAmYi4NQC1UgDIcJSdIjiz1deb2XzKIE6zZpj4oxZusLXKkTlNa613WnTpMWsceN0sU/BvHlsr0yt5531KIui1i8OQIIECbQLwkQTjExL4Pip0+g3cqTaLIvu/5dff9W+yoI2UVkc27kdXzdtArHR1hOMSMCEBChQYzCosrp18cpV+LpbD4gpS/m69XTHGXm9dT/Ks4v4GhWbTrGjO7h1Mw6HbEWb5s201gv/93+o7NsQN0zoIEFmJPWqV9N+rggKxtVr1zTNyFwExMa6fa/eqFCvPuYGLMGt27e1g/IDce7ECWpyJSoLzWREAiYnQIEajQEW5wYDRo9B534D1ZmCOFXoNnAQxMXg1WvXtSTRg3qXKAHRKW5dsQz7t2xSm07x9PJh8uR6TZevW+siHvlw8bffUKNJU0kaLMS8Oc18fXUxlrz+nh2wOOYFsgTDEAjavFlNuep/1UrXAVgbVtHbWxcaiQqjVHEPazaPJOASBChQX3OYr1pmWAW8y2H2wkVYumY1ZKWu9VbZKkpsNFfNn4fTe/dg9oRxKjC/+PRT6yUvHEXgWvdSvWIp+4ULTJAhetQKpUtrT8Q1otUfq2YwcjoC8tZFxlHWBLTu2l2djVg70ahuXexZH4Rpo0ZwoZEVCo8uR4AC9TWGPOLECZSt64Mr167q1WlSpYIsHJIFRGf27YFsZixehGSBkV7wmlELP1+98saNGxCTGv1gsqhN8ybaI3GJuHjlak0zApyJgTybzdp3QJladXRxndXrV6JE76j+X35EDurRDenSpHGmbrGtJBDrBChQ/wWp+K6t1aSZmraI16MJQ4dg38b16NOpo5q4JIxaePMvxbz0dM7nTAYORES89Bpnz5RZeKF8ebUb0+bNg2waoB8YGZ6ALCwSj0Y5PL2wefsOm7OOjB99hGG9e+HU7l26Ql3UHIbvDBtIAnFAgAL1HyDLF/+QceMhu6uI60BZXLRy3hxUr1D+H+6IfrY40reuhJVZcPRLcI47Wvr5aUPFd+v6rVs1zci4BMTcS7xdFatYWT0aPYny1JU+XTqIT2fZbKFBrZrG7QDYNBJwDAEK1Jdwv3PnLnxbfw2ruUfOrFmxMXAx5PiSy2OUZTVsP3oi0l4vRoUZ9GYvj2L4NGMGbd2kmXP0yMhYBGTBnbyNEbeAYu4l3q6khfHd3SGOSYICFmJX0Fr16Sz5DCRAAi8SoED9GxNxQiAmAGIOIKdkRioz0+ftRyU/toLYbEpZh48fk4Mpg5ubG1o2aqR9E1/Gu7/fr2lGjicg+tFpc+ehSPmK+jbmWNQGDmIv2sKvIXZvCMKUEcNgfU4d32K2wNEEWP8/E6BAfY6NbJFWqX4DnP+//4M4tO/buRNEZyq60+cui9VkzqxZtLyr165DXonqBxNGNStVRMKEkY4e+gwbbsIeOleXrPrR/GXKYNiEibZnT1Zm9+vcGd9v2qRbpxnZ5aVzEWdrXYEABWrUKE+dMxdN2rXXHTDEKcGCKZPRzLdB1Fn7HXJYXidbSzezHlV+lOTLkVO7+qdJzYS0cwaPwg8eQrP2HXUPW9nxRfbalSbnzZlTt+QLW7cWTX3rI9E7CSWbgQRIIBoEYi5Qo1GZES+VBUetunTD8ImTdAXqpxkzYsOSxZCt1+KivRnSpbO5Yzsa9botLup1RB1VoxZ03bx507RmQrHNVZzMX/rjd4hrv207d6Hn0GGYvyQQou+UsHxdEHoNHY7A1av1eO/evRea8Lx+tHbTZti8fbs+68/rR1fNnwvZxShePJf/SniBHzNI4HUJuPT/nt9+v4xqjfwRvGWL8pLFM0EBi5AuTWr9HFeRdWFSxPHjcVWlQ+rJnuVLW72HTd5XW0dfkTj783l0HzwY4kx+xKTJEK9bTdt1sDyTjXUGmdWjOD4rUAgFy5RX137+bdti4dJl6DN8hOo7ZQV6xz59sWDpUnTpP1CPeb3Lajk9Bg9RIdumR08UKlder7fqRxMnekdnoWHB66gffcX48BQJRJeAywrUgxEREN+7J06fVmbiX1d8jzriVVfOrNm0DS8RMppvlijTp5/ZNgCIOGbuHw8vGzPRzS9buw4i7EpWrQ7P6jUQsHwlxJn8lNlzIH6ht+zYgUMRRyHXyoKhl5Xzqry7d+9qOYuWr1Ahu2bDRli3B0ybKhVkXcB+yw9I0ZPK51eVxXMkQALRI+CSAnXpmrWo3aQZrt+4CXHMMGv8WIh/XTc3t+jRi6Wrc2TJrCXJF6gsFtEPJozkdWLSxIm1Z4Fr1ujRzJHMCMVh/FeduiBPKW+ddXbq2w8i7M5duGDr+n/i/wfpUqfWlbSexYqiZqVKkBW2Pdq3w+gB/SE/9NYs+A67LDPKg9u2qntL8U5kDYdCQ1Agd25beX9PpE6ZSvWju9cH6boAR/xo/Hub+JkEzEjApQSqbKHWe9hwdO7XH6JXkv071y78DmVKlnTo2D7vMenoiRMObYu9K0+ZIoVWkThxpGDVD46KYrFe0cXv2b8fE2bMRINWrZClaDGITWe/kSOxfts2XLka6bZSFmfJAqBW/o1VUO5ctwZnD4Rjz4ZgBAUshLizHDd4oK6wbdW4EepUrQJxMp87ezakT5sWH36QDOKZ6PmQ/P33sHzubIhgfT5YBW74pvXUj8biWLMoEvgnAi4jUGU2Wq/lV/gucKmykC+1DYGLkemzz/SzIyMxTfgg2fvahAgTO3iQDqa1vHaUY5qUKeXgtOHGzVsQ5weDx45DFd+GyFzUAz7NW2LM1GkI2xuOO3fvad/EnlNmnd3afAPx+XxqdxhkAVCPdm1VUIobP70wFiIRrM8Hq9CNhaJZBAmQwGsQcAmBeuann1RfKi7VhEnDOrWxbM4svP/euzDKX65skXpUM3tMEtZPnj6VA54+e6ZHZ4kuXLyI5evW6YIfz2rVkaNESYh7vhnfLcCR4yfwOMo9n/w4qlKuHAb36I5Ny5bg+M4dOuuUzbVlV6K33nrLWboc03byfhJwOQKmF6hiIlDF1w+//X4ZYiYgOqkhPXto2kijbfVEY+aFSbL914HDhxX7T+fO6dGIkfhxFjMV0X+KSVU+7zLwqFQFHfv00wU/Z89H6j/d3NwgW/SJX1txALLX8to2fPMGTB4+FH5160A2BnBzc4xe3ohc2SYSMDsB0wrUZ5YZkLx+k1mEfJHLbFRmpaKTMuKg5oxy8CB7hp49f96ITYxRm0RIte7aDbfv3tVysn75PxMazXBg9Hf9ZzaP4mqmIvpPMamyrpL9n/6zkeo/Zfa5dcUy3XmleoXySJs6tQN7wapdigA7a0gCphSod+/dh3/bdrpARASr6ElFXyp6U0OOgqVRVoFqSSLC8gpRjmYKomvctjNMu+Rfrx6mjxmlaUdEMdd/tlP9p+hHHdF+1kkCJGBMAqYTqBd/uwTxxyt+eQV5RW9vyEpeWdErn40aZFGSdcFOxElzrfQVM6VZCxcpelmx2r9rZ03HVUT9Z1yRZj0kYAoCb9wJUwlUWXRU3qce5JWp2Dx2/eZrTBs1Qm1N35hQHN5o1aOaaWGSrHgVD0CCUXSK00aOgJub/fSK8mqZ+k+hzUACJBDXBEwjUOcsWgwxi7l565Y69p4zYTy+adY0rnnGqD6rPaqYzohgiFFhBrj5p59/RvOOHSD2v7L6deG0yUiQIHLHmdhq3vP6T99WrUH9Z2yRZTkkQALRJeD0AvW3S5dR3a8x+o8apV/cYtcXFLAIXh7FosviH6+PqxM5o7ZyExOM0z/9FFfV2qWeHyztr96wMWQ3E7GHXDR9Kj5MnjzGdYn+c8DoMeg5eAiq+TXC5wUL2+w/d+7dZ7P/FH+18gyIB6xls2fh7P7wKPtP6j9jPAgsgARI4KUEnF6gNmjdGgePHtXOyQ4xQQELITvGaIaTRTmyZLW12Jlf+4q9ZoV6vrh557a+3p05dhw++/hjW9+ik5AZqAhK2bOzvE99tf+cbdHHLly+AoeOHrMVlSpFClQuWxYDunXFxqVLcHL3LsybNBHio7lg3jy265ggARIgAXsRcHqB+qtlhipwsn6ZCQunTkHSJEnko1MGWTX6cfr02nZn3Bv1zytX0LhtW7XXfPjoofajTtWq8ChcUNMvj17MPXzsOCbPmo26zVroDFRe5U6bOw/WjQzkDnFhKLaeYvO5Z30wvt+8UXdO8a/ngyxffCGXMJAACZBAnBJwaoF64Gm1auIAAA6YSURBVMgRiN2mEOvy9deQhUiSduaQI8pR/tGTJ52qGyuD18OrRi2E7Nyl7f40YwYEW169j+rfVz+/Kjp7/gLmBwaq56FsHiVQtaEfRk6egr0HDthuky31fKpXU6cJEdtDsd8iQMUbkXglknO2C5kgARIgAQcRcGqBGrJrt2ITg3uPQtGbBemNBoxyRrkgPPXDjzZ3dgZspq1J53+5iFK1aqF9r96QBWFubm5o3cQfm5ctRfaoHwe2i6MSV69dgwhg8TxUsEx5eFarjj7DRqhv3Fu3b+tV4oijQunS6jQhLGgtZBY6sl9fiACVc3oRo38lwAtIgATijoBTC9TQsMjZUNEC+SFCNe6w2a+mHFmyaOGyMOnEmTOaNmp07/591PT3x48/ndMmfpIhg9r8dm/b5i/jIY42tu7ciX4jR6J0zdrI7VVaBbDoWi/98bveK6t/5dVwj3btsH5xAI6EhuDb0SMhbv0ypEun1zAiARIgASMTcFqBevXadVgFjmexYkZmHK225bDM6qyvro3sMUmEqX+bdvgzaluyfLlyYcvypciZNavOrMMPHtKNs6s38kd2j+Jo0rY9xDfuD2fPKg93d3fkypZVTZuWzJyO4zu3Y9G0aWjl3wjZMn+pi5n0QkYkYFgCbBgJ/JWA0wpUmfFYuyLmEda0sx9lpmZdEWtUPaoI0Qo+9Ww6Ttnbc3DP7pi3JBCNvmmjtqC1mzbD+OkzcDAiAo+fPNFh+dSiV21Uty5mjB2NoxY96NqFCyDON4rkzw/uwqKIGJEACTgxAacVqNbXvfKa0WyvBHNG2aOKgwcjPVuiL/WzCMwCZcvj3IVftGmff/IJlq5Zg3J1fDBozFiEWvTaYnsqJ1N8mBw1KlbAmIEDsH/LJoSuXoVBPbqhnJcXZEWzXMNAAiRAAi8j4Ix5TilQxfNO6O7dyrtksSJ6NFOUI0qg/njunG0Vs6P7J694y/v4YLtFYD55/NjWHGmjvH6XDHHgULp4cfTr3Bmbli3BgS2bMX7IYNSuUhkpP/xQLmEgARIgAdMScEqBuv/wEciWbDIqXsU85GCqkDNrNu2PuB88duqUph0dla1dF3fv3XuhGflz50aHr1pi5bw5OL13D+ZMHI+mvvV1L9AXLmYGCZAACZiYgPMI1OcGIXR35OrehAkSoHC+vM+dMUcy25eZbDa1R08YQ6CmiJphvv/ue2je0BfzJ0/CmX17sGLubBWo+XLlMgd89oIESIAE3pCAUwrUkLDI171FCxT4i3nGGzIw3G3x48dHlkxfaLsiThzXo6MjEZx7N65HxI4Q9OnUEZ7FijrNLj6OZsf6SYAEXIOA0wnUy3/8gTM//aSjI1/qmjBhlCNLpF/foyfjZIb6WgTTpkr1WtfxIhIgARJwRQJOJ1BDwsJs4+RdsoQtbbaEdaXvuQsXcPv2HbN1j/0hARIgAdMRcEKBGvm6V8w1UqVIYboBsXbIutJXPh875Vx+faXNDM8RYJIESMAlCDiVQBVzmbB9+3RgzOTMQTv0tyjz55/D3aJLlewjx0/IgYEESIAESMDABJxKoO7df8BmLuNZ1Hz2p88/J+J+8L2kkVvRrQgKfv4U0yRAAv8jwBQJGIaAUwnU0ChnDmIuUzCv+cxl/v5UPH4c6bIvVQo6Rfg7G34mARIgAaMRcCqBGhK1u0yJIkXg7u5uNJax2p5r12/odmhSaJ1q1eTAQAIkQAJxS4C1RYuA0whUMZc5e/68ds7M5jLaQUv0/eFDljjyX+7s2SITjEmABEiABAxLwGkE6qbQUBvEMiVL2tJmTRw+FunQIXHiREifNq1Zu8l+kQAJkIBpCERToDqu37KLidSe+fMv8EGy9yVp6nAkSqAWyJ3b1P1k50iABEjALAScQqA+evQIYfvClbmnR1E9mjkSp/iHj0fOUHNl4+teM481+0YCJGAeAk4hUHd/vx8iVAW7V7FicjBlsHZKtkR78OCBfsydPbseGZEACZAACRibgFMI1NBdkbvLJEmSGHlz5jA20VhonVV/KkXlzWH+/ko/GUiABEjA2Qk4hUC1mssUL1TY9OYy8kBZ9aefZMgAWZQkeQwxJcD7SYAESMC+BAwvUH/+5RdcuHhRKXh5mP91r3TUOkPNRXMZwcFAAiRAAk5BwPACNTRq71Oh6Qr6U9GdnjkbuT0dFyTJqDM4AwG2kQRIADC8QA3ZFbldW/YsmV3DXOb4CcgqX3k4c3OGKhgYSIAESMApCBhaoMrK3r0HDipIz2LmN5eRjlpf98aPHx9ZM2WSLAYSIAGXJsDOOwsBQwvUnXv32cxlPIu6hv40Isr+NIdlRi5C1VkeJLaTBEiABFydgKEFashz5jJ5criGPaZ1hsoFSa7+X5P9JwESiAsCsVmHoQXqlu07tK+lihWDm5ubps0cyQ4zl/74XbuYOzvtTxUEIxIgARJwEgKGFajiLUh2mBGOJS0CVY5mD9xhxuwjzP6RAAmYmYBhBWrort3K3c3NDd7Fi2s6TiIHVmJ93SvOHNJzhxkHjgSrJgESIIHoEzCsQA2JEqi5smWFuByMftec7w6rhyTuMON8Y8cWkwAJkIAhBer9Bw8QftBqLlPMJUZJbE9dYIcZlxhLdpIESMA1CRhSoO7YswdPnjzREXEV+1PRGYuXJOl0bu4wIxgYSIAESMCpCBhSoG7ftUchykbiObJk0bTZI6v+VPqZlzvMCAaG6BLg9SRAAg4lYEiBGhJlf1qyaFGXMJeRJ8CqP+UOM0KDgQRIgAScj4DhBOqpH3+A1VzGy0XcDcpjY52h5qL/XsHBQAJGI8D2kMC/EjCcQLXuLuPm5oaSRYr+awfMcIHoTrnDjBlGkn0gARJwZQLGE6i7I+1P8+bM6TrmMtxhxpX/D7LvJEACJiFgKIF6+/YdHDgSoWhd6XVv+MFD2md37jCjHBiRAAmQgDMSMJRA3blv7//MZTxcw/5UHpolq1fLAcneTQruMKMoGJEACZCA0xEwlEANCdulAD9I9j6yZsqkabNHO/bsxa+XLmk38+fOo0dGJEACJEACzkfAWAI1ylymtIv47n38+DF6DRmqT02KD5Nj3OCBmmZEAiRAAiTgfAQMI1CPnzqNq9euK0FPF3ndO23uPPzy66/a54HduyFhggSatnfE8kmABEiABGKfgGEEqvV1r7u7OzyLmt9c5rffL2Py7Dk6okULFkSFUqU0zYgESIAESMA5CRhGoIbujtSfyk4rrjBT6z9iNGQTAFmENKJvb+d8etjqlxBgFgmQgKsSMIRAFXOZQ0eP6RiIu0FNmDjaHR6OjSEh2sMWfg2RnnufKgtGJEACJODMBAwhUEN278azZ8+Uo5eHuV/3ykKkbgMHa19lIVK7Fs01zYgESODfCfAKEjAyAUMI1NCwMGWUKkUKZPrsM02bNeJCJLOOLPtFAiTg6gQcLlBlZrpl504dh1LFPfRo1ogLkcw6suwXCZiBAPsQUwIOF6hHjp+A6FClI54m312GC5FklBlIgARIwJwEHC5Qt1v0p4JWzGU8ChWSpCkDFyKZcljZKRIgARKwEXiVQLVdZM+E1f60cP58pnVswIVI9nyCWDYJkAAJGIOAQwWqeEY6evKkkvAqZl5n+FyIpEPMiARIgARMTcChAnXjtm02cxlPk+pPT5w5g/HTZ+pD9BePSJrDiARIgARIwCwEHCpQZyxcqBwTJkyATzNm1LRZIlm9PD8wEFV9G+HR40eI5+aGob16mKV77AcJkAAJkMDfCDhUoH6WIVKI3r//AFZd6t/a55QfZVZaqYEv+gwbgYePHmofvEuWxMfp02uakd0JsAISIAESiHMCDhWo00aPxCcZMminO/cfgLv37mvaWaM7d+6qEK1YrwGOnTyl3SiYNw/CgtZi5rgx+pkRCZAACZCAOQk4VKC+9dZbGDsocg/QK1evYviEiU5LedX6DShetRrkNe/Tp0/xYfLkmDhsKJbNnoUM6dKBfyRgGgLsCAmQwEsJOFSgSovy5MiOejWqSxLfLV0Kq5N8zXCC6MLFi6jdtBna9ewF+VEQL148NPapix2rV6Fa+XJO0AM2kQRIgARIIDYIOFygSid6d+iA5B98oCt+O/bpi8dPnsDof//9738xcvIUeFWvifCDh7S52TJ/iQ2BARjYvRsSJ06keYxIgARIIBoEeKkTEzCEQE2SJDEGde+qGM9duIAps+do2qjRjj17UaJKdUyeNRuPHj1C0iRJMKRnDwQHLELmz78warPZLhIgARIgATsSMIRAlf5V9PZG8cKRrgcnWQSVCFbJN1IQ5/bN2ndEw9ZfQ9LSthqVKmLHmtVoWKc23NzcJIuBBEiABEjAiATs3CbDCFTp56gB/ZDonYR4+PAh5NWv5BkhyCto8XbkWbUGNm/frk36NGMGrJo/F+MHD8IHyd7XPEYkQAIkQAKuS8BQAjV1ipTo1ratjoYsTgpYuVLTjowORkTAu2YtDJswEfcfPFB/wz3atcWWFcuRN2dORzaNdZMACZAACRiIgKEEqnBpVLcOZHGPpPuPHI3fLl2SpJ3CPxd76dJlVPXzQ/VG/jh7/oJeWKZkSYSuWYlW/o0R391d8xiRAAmQAAmQgBAwnEB1c3PDhCGDVR/5wDIjrNSgoW2/VGmwvcOBI0fQuV9/FK5YCYePHtfqZOY8b+JEzBo/FmlSptI8RiRAAiRAAiTwPAHDCVRp3OeffIKSRYpKEleuXUPdFi3sKlRlg/PZCwNQsmp11GjcBEvXrIU4Z5AGFMqXFzvXrYZXcfPuhiP9tEdgmSRAAiTgSgTiGbWz8yZPQM3KlbR5x0+dRp1mzSGu/TQjliLRj3bo0xd5vctgwOjRsK4sFjOeRnXrYtvK5Vg6aybefvvtWKqRxZAACZAACZiVgGEFqpubG8YOHGATquJwXjwSxVSoymx07uIlKF2ztupHV6wLgrxalgEWr01jLHUe3LIZg3p0g8yUJZ+BBIxHgC0iARIwGoH/BwAA///1aFkaAAAABklEQVQDAAwoR3e7s/7TAAAAAElFTkSuQmCC</t>
         </is>
       </c>
     </row>

--- a/visitors.xlsx
+++ b/visitors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mr. Kishore poonamalle</t>
+          <t>Career Craft Academy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -507,7 +507,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mr.Javid</t>
+          <t>Vaanigar International Pvt Ltd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -539,7 +539,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dr.D. Nagarajan</t>
+          <t xml:space="preserve">NIT Trichy </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. D. Christopher </t>
+          <t>Morais Group</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -607,7 +607,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mr. Surya prakash</t>
+          <t>Teknospot</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -639,7 +639,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr. MJ Rajesh</t>
+          <t>RASA Management Pvt Ltd</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -671,7 +671,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mr. Kiran kumar</t>
+          <t xml:space="preserve">Dorus Tree </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -703,7 +703,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mr. Kishore poonamalle</t>
+          <t>E Sales</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -735,7 +735,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mr. Dinesh Ponraj</t>
+          <t xml:space="preserve">Dorus Tree </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -767,7 +767,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mr. D. Vasudevan</t>
+          <t>OASYS cybernetics Pvt Ltd</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -799,7 +799,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mr. Anand Pitchaikani</t>
+          <t xml:space="preserve">Modelon </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mr. Niyamath</t>
+          <t>Thinkin Lab</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dr.Suresh Kannaiyan</t>
+          <t>Menmozhi Technologies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -903,7 +903,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Er. Kesavan</t>
+          <t>Quantanics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mr. KC. Divaagar</t>
+          <t>Vast Brick</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -971,7 +971,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mr. P. Umasankaran</t>
+          <t>Startupnewstamil</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mr. Vignesh</t>
+          <t xml:space="preserve">Real List </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1035,7 +1035,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mr. Ajay jayaraj</t>
+          <t>CII Trichy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mr. Felix</t>
+          <t>CII Trichy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mr. Karthick</t>
+          <t>Primo Motor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1133,11 +1133,7 @@
           <t>24.09.2025</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Mr. Kesavan</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>9087940111</v>
@@ -1161,11 +1157,7 @@
           <t>24.09.2025</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Mr. J.B. Shriram</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>9965240023</v>
@@ -1185,11 +1177,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Mr. Velmurugan</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>9442250757</v>
@@ -1211,7 +1199,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dr. Sanakara Ram</t>
+          <t>Anna University Trichy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1247,7 +1235,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dr. B. Chagun Basha</t>
+          <t>Goverment Of India</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1279,7 +1267,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mr.A. Irudayaraj</t>
+          <t>Pharama Industry</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1311,7 +1299,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mr. Shree Balaji</t>
+          <t>Hi Life.ai</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1347,7 +1335,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mr. Vinoth kumar</t>
+          <t xml:space="preserve">Land Market </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1383,7 +1371,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mr. Bathrivishal</t>
+          <t>Saranathan Engg College</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1415,7 +1403,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mr.M.Vinoth Kumar</t>
+          <t>EDII TN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1451,7 +1439,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dr. Girivasan</t>
+          <t>CREASER PVT Ltd</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1487,7 +1475,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mr. I. SaratKumar</t>
+          <t xml:space="preserve">Crypto Graphics </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1523,7 +1511,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mr. V. Gokula krishnan</t>
+          <t xml:space="preserve">EGS PILLAY group of insititution </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1555,7 +1543,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mr.Ravishankar Rajagopalan</t>
+          <t>Augur.Ai</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1591,7 +1579,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dr. Sandhya Chintala</t>
+          <t>NASSCOM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1627,7 +1615,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mr. Tharvesh Muhaideen</t>
+          <t>TM NEXUS HUB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1663,7 +1651,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mr.Rajendran</t>
+          <t>ZOHO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1695,7 +1683,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mr. Divagar KC</t>
+          <t>Vast Brick</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1731,7 +1719,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mr. Karthick</t>
+          <t>Primo Motor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1767,7 +1755,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Er. S.Xavier</t>
+          <t>CHEN AI DIGITAL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1803,7 +1791,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mr. Sarath kumar</t>
+          <t xml:space="preserve">Crypto Graphics </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1839,7 +1827,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mr. P. Vinothkumar</t>
+          <t xml:space="preserve">Land Market </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1875,7 +1863,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mr. Titus Ricard</t>
+          <t>Give Life</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1911,7 +1899,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dr. Sanakara Ram</t>
+          <t>Anna University Trichy</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1947,7 +1935,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mr. Praful Manuel</t>
+          <t>Chillout Studio Pvt Ltd</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1983,7 +1971,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mr. Muthamizhan Selvaraj</t>
+          <t>UPRP 360</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2019,7 +2007,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mr.Siva Tamilvanan</t>
+          <t>Cybernerds Solution Pvt Ltd</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2055,7 +2043,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mr. Siva</t>
+          <t>Ztore Spot</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2091,7 +2079,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dr.SAikrishna Vaidyanathan</t>
+          <t>Mountain Lamp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2127,7 +2115,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mr. P. Mark Marimuthu</t>
+          <t>Amazing Ads</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2163,7 +2151,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mr. Pradeep Kumar</t>
+          <t>Nanosoft Technologies</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2199,7 +2187,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mr. Gunasekar</t>
+          <t>work from heaven</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2235,7 +2223,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mr. Ajay Sharma</t>
+          <t>work from heaven</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2271,7 +2259,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mr. Velmurugan</t>
+          <t>Taxi Na</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2307,7 +2295,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mr. Balachander R</t>
+          <t>Startup Singam</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2343,7 +2331,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dr. Vigneshwar</t>
+          <t>Routabit</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2379,7 +2367,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mrs. Nusrat Fatima</t>
+          <t>Routabit</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2415,7 +2403,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr. Dinesh Babu </t>
+          <t>Daffytel Technologies</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2451,7 +2439,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mr.Shiva</t>
+          <t>Nerdshive</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2487,7 +2475,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Karuppanan </t>
+          <t>Startup TN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2523,7 +2511,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mr. Shree Balaji</t>
+          <t>Hi Life.ai</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2559,7 +2547,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mr. Andrew Anand</t>
+          <t>SWARMX Advanced Technologies</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2595,7 +2583,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dr.Manochandran</t>
+          <t xml:space="preserve">BIM </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2631,7 +2619,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mr. Vinoth kumar</t>
+          <t xml:space="preserve">Land Market </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2667,7 +2655,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mr. Balamukesh</t>
+          <t xml:space="preserve">Land Market </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2703,7 +2691,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mr. AjayJayaraj</t>
+          <t>CII Trichy</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2739,7 +2727,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mr. Benard Shaw</t>
+          <t xml:space="preserve">Cogan Valley </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2775,7 +2763,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mr. Arun Rebero</t>
+          <t>CONTURA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2811,7 +2799,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mr. Karthick</t>
+          <t>TENSORDRIVE AI Pvt Ltd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2847,7 +2835,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Naveen Krishnamoorthy</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2883,7 +2871,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>P.L NatchiAmmai</t>
+          <t>Mookambigai Engineering College</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2919,7 +2907,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mr.Anandha Kumar</t>
+          <t>L.F Audit Trichy</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2955,7 +2943,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mr. Neelakandan</t>
+          <t>L.F Audit Trichy</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2991,7 +2979,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t xml:space="preserve">Bon Secours College for Women </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3027,7 +3015,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dr.VR.Sarma</t>
+          <t>Han Tech Pvt Ltd</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3063,7 +3051,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mohan K</t>
+          <t>Startup Founder</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3099,7 +3087,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mr.RaguPrasath</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3135,7 +3123,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mr.Shree Balaji</t>
+          <t>Hi Life.ai</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3171,7 +3159,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Adhithi</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3207,7 +3195,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mr. Gokul Karat</t>
+          <t>Mechinex Automation Pvt Ltd</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3243,7 +3231,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mrs.Anisha</t>
+          <t>Soulvai. Technologies</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3279,7 +3267,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dr.Selvamani</t>
+          <t>Anna University Trichy</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3315,7 +3303,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mohan K</t>
+          <t>Startup Founder</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3351,7 +3339,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mrs.Anisha</t>
+          <t>Soulvai. Technologies</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3387,7 +3375,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mr. Vinoth kumar</t>
+          <t xml:space="preserve">Land Market </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3423,7 +3411,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mr.Parthibpan</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3459,7 +3447,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mrs. Kanmanisureshkumar</t>
+          <t>Spark Digital.Ai</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3495,7 +3483,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mr. P.Anand Kumar</t>
+          <t>Anna University Trichy</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3531,7 +3519,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Adhithi</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3567,7 +3555,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mr.RaguPrasath</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3603,7 +3591,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mr.Avinash Kannan</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3639,7 +3627,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Adhithi</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3675,7 +3663,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mr.RaguPrasath</t>
+          <t>Gullix Pvt Ltd</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3706,47 +3694,1303 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>13.05.2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Parthipan</t>
+          <t>VMRF Salem</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>innovation</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>6374532706</t>
-        </is>
+          <t>VMRF Salem</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>9789243415</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>dranusuya12@gmail.com</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VMRF Salem</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VMRF Salem</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>9566658559</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>anbu80@gmail.com</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>16.05.2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DigiPlus </t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DigiPlus </t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>8056977938</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>bharath@digiplusagency.com</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>16.05.2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Profrontend UK Limited</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Profrontend UK Limited</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>7305484337</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>anantha.ganesh@profrontend.co.uk</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>16.05.2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DigiPlus </t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DigiPlus </t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6374282263</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>snsanjai8@gmail.com</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>8508770550</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>exploretrauell@gmai.com</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>9952650864</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>exploretrauell@gmai.com</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>30.05.2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AUKR Moringa Promise Wellness</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AUKR Moringa Promise Wellness</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>8489643471</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>moringapromisewellness@vanuagmail.com</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>30.05.2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AUKR Moringa Promise Wellness</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AUKR Moringa Promise Wellness</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>9972650864</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>moringapromisewellness@vanuagmail.com</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>30.05.2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AUKR Moringa Promise Wellness</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AUKR Moringa Promise Wellness</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>9972650864</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>moringapromisewellness@vanuagmail.com</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>30.05.2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Arkwell Lifesciences</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Arkwell Lifesciences</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>9842580088</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>arkwellnutrition@gmail.com</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>02.06.2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Startup Founder</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Startup Founder</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>9043610553</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>vigneshlakshmanababu@gmail.com</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Nexwear Innovation Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Nexwear Innovation Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>8190907213</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>founder.nexwear@outlook.com</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mookambigai Engineering College</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Mookambigai Engineering College</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>7708235835</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>staffmceece@gmai.com</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Aliyar Agencies</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Aliyar Agencies</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>9976294532</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>azarksa12@gmail.com</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Azohos App Studio Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Azohos App Studio Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>9942952654</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>darwinberrabha@azoho.in</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>8508770550</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>exploretrauell@gmai.com</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Trauell Immersive Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>9952650864</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>exploretrauell@gmai.com</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Suranathan.SAS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Suranathan.SAS</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>9965690081</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>bathri06vishal@gmail.com</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sastra University </t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sastra University </t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6380035064</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gullix Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Gullix Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>9003338588</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>adhithitamilselvan@gmail.com</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Gullix Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Gullix Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>8870582726</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>raghuprasath12@gmail.com</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Blackwins Tech Solution LLP</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Blackwins Tech Solution LLP</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>9360759463</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>lavanya.works@blackwinstech.com</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Blackwins Tech Solution LLP</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Blackwins Tech Solution LLP</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>7708139259</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>kavin.works@blackwinstech.com</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>KAA MAA Techologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>KAA MAA Techologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>9043777296</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>karthickmari.p.tchai@kaamaa.com</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felamity Technologies LLP</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Felamity Technologies LLP</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6374008802</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>business@felamity.com</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kiwiston Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Kiwiston Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>8946090047</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>info@kiwiston.com</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Kiwiston Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Kiwiston Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>9600983754</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>saranprakashsp@gmail.com</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kiwiston Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Kiwiston Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>9442205483</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>info@kiwiston.com</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Anna University Trichy</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Anna University Trichy</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>7598237063</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>jennetdehora@gmail.com</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Profrontend UK Limited</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Profrontend UK Limited</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>7305484337</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>anantha.ganesh@profrontend.co.uk</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Career Designing Solution</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Career Designing Solution</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>8925448089</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">profnallucds@gmail.com </t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DigiPlus </t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DigiPlus </t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6974282263</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>snsanjai8@gmail.com</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bhoothi Green</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Bhoothi Green</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>9880210680</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">profnallucds@gmail.com </t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>09.07.2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Nexwear Innovation Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Nexwear Innovation Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>8790907213</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>founder.nexwear@outlook.com</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ascdvfbgnhm</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>sdafghj</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>63745327006</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>parthipancseai@gmail.com</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Coimbatore</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAogAAAC2CAYAAABapnxOAAAQAElEQVR4AezdB3xT5d7A8X8SQFCv48pQhoCKrxsREVBABcFS9i5Llt6ryNDrVUBwoQy9ehVB1CtTAaFQyiwoAooI4gC3ILJBNiKbtknf8zxp0gIdaZOcnJP8/DRPTs54xvfpR/59znmeODNSj2TwwoDfAX4H+B3gd4DfAX4H+B3gd8D3O+AU/kMAAQQQiEIBmoQAAggUXoAAsfB2XIkAAggggAACCESlAAGihbuVqiGAAAIIIIAAApEQIECMhDplIoAAAgjEsgBtR8DyAgSIlu8iKogAAggggAACCJgrQIBorjelRYsA7UAAAQQQQCCKBQgQo7hzaRoCCCCAAAIIFEyAs70CBIheB1IEEEAAAQQQQACBTAECxEwI3hBAIFoEaAcCCCCAQLACBIjBCnI9AggggAACCCAQZQKWDBCjzJjmIIAAAggggAACthIgQLRVd1FZBBBAwNYCVB4BBGwiQIBok46imggggAACCCCAgFkCBIhmSUdLObQDAQQQQAABBKJegAAx6ruYBiKAAAIIIJC/AGcgkF2AADG7BtsIIIAAAggggAACQoDILwECUSNAQxBAAAEEEAiNAAFiaBzJBQEEEEAAAQQQCI9ABHIlQIwAOkUigAACCCCAAAJWFiBAtHLvUDcEEIgWAdqBAAII2EqAANFW3UVlEUAAAQQQQACB8AsQIAZqzHkIIIAAAggggECMCBAgxkhH00wEEEAAgZwF2IsAAucKECCea8IeBBBAAAEEEEAgpgUIEGO6+6Ol8bQDAQQQQAABBEIpQIAYSk3yQgABBBBAAIHQCZBTxAQIECNGT8EIIIAAAggggIA1BQgQrdkvedbqxIkTMnj4SFHveZ7IQQQiL0ANEEAAAQRsKECAaMNOa9i2vXyQmCjq3YbVp8oIIIAAAgggYHGB/ANEizcgFqt38tQp3Wzfu/5AggACCCCAAAIIhEiAADFEkGZmc+z4cV3cocOH5dCff+ptEgQQQKCgApyPAAII5CZAgJibjIX3X3D++bp2Ho9H4jok6G0SBBBAAAEEEEAgVAIEiKGSNDGfYkWLZpYmcvp0qn+bDQQQQAABBBBAIBQCBIihUDQ5jxIlSvhLvLpSJf82GwgggAACUSJAMxCIsAABYoQ7oDDFX1Wxor6sXu3aMmr4ML1NggACCCCAAAIIhEqAADFUkhHIR91qrlCubARKpsgABDgFAQQQQAAB2woQINq266g4AggggAACCJgvEBslEiDGRj/TSgQQQAABBBBAIGABAsSAqTgRAQSiRYB2IIAAAgjkLUCAmLcPRxFAAAEEEEAAgZgTsGmAGHP9RIMRQAABBBBAAAHTBAgQTaOmIAQQQACBfAU4AQEELCFAgGiJbqASCCCAAAIIIICAdQQIEK3TFwWrSUbBTjfxbIpCAAEEEEAAAZsLECDasAM3bt4i4hDR78J/CCCAAAIImCFAGbEkQIBow97OyPDoWrvd6fqdBAEEEEAAAQQQCKUAAWIoNU3K68oK5XVJl5cpo99JEAhUgPMQQAABBBAIRIAAMRAli53jcnq7zeNxW6xmVAcBBBBAAAEEIiAQ8iK9kUbIsyXDcAq4XC6dvcfjvdWsP5AggAACCCCAAAIhEiBADBGkmdk4Hd5ucxMgmslOWQiEV4DcEUAAAQsJeCMNC1WIquQv4B9BdDOCmL8WZyCAAAIIIIBAQQUIEAsqlvv5ph1xOb3dxgiiaeQUhAACCCCAQEwJeCONmGqy/RvrdHmfQXS7maRi/96kBQggYH0BaohA7AkQINqwz33PIDKL2YadR5URQAABBBCwgQABog066ewqulwOvcvj4fv2NEQACacggAACCCCAQOACBIiBW1nmTKeTW8yW6QwqggACCCAQSQHKDpMAAWKYYMOZrcvl7TYmqYRTmbwRQAABBBCIXQFvpBG77bdly10u7wiih2VubNl/VPosAT4igAACCFhOgADRcl2Sf4WcTm+A6M5gFnP+WpyBAAIIIIAAAgUVCEWAWNAyOT9IAZfL221uRhCDlORyBBBAAAEEEMhJwBtp5HSEfZYVcDq8s5gzMvgmFct2EhVDICoEaAQCCMSqAAGiDXveyQiiDXuNKiOAAAIIIGAfAQJE+/SVv6YuZ+YziJ78n0H0X8QGAggggAACCCAQoAABYoBQVjrNlTmC6OGr9qzULdQFAQQQMFOAshAIqwABYlh5w5O50+kbQeSbVMIjTK4IIIAAAgjEtgABog373+XKDBAZQbRh72WrMpsIIIAAAghYVIAA0aIdk1e1XE5vt2VkMIKYlxPHEEAAAQQQiIRANJTpjTSioSUx1AaHw7vMjdsYQSRIjKGOp6kIIIAAAgiYJECAaBJ0KItxObO6je9jDqUseSHgE+AdAQQQiG2BrEgjth1s1XrfM4iq0sxkVgq8EEAAAQQQQCCUAlEbIIYSyWp5+WYxq3oxgqgUeCGAAAIIIIBAKAUIEEOpaVJeLldWt/F9zCahUwwCCFhFgHoggIAJAlmRhgmFUURoBFxO7zI3KreMDI9644UAAggggAACCIRMgAAxZJTmZeS0+wiieVSUhAACCCCAAAKFECBALARapC9xOr3L3Kh6qKVu1DsvBBBAAAEEIi1A+dEjQIBow750ZbvF7PG4bdgCqowAAggggAACVhYgQLRy7+RStzNuMXt4BjEXJnYXSoCLEEAAAQQQECFAtOFvwRkjiExSsWEPUmUEEEAAAQRMFihgcQSIBQSzwumubJNUPO4MK1SJOiCAAAIIIIBAFAkQINqwM7OPILp5BtGGPUiVESiUABchgAACpgkQIJpGHbqCHM6sbmMWc+hcyQkBBBBAAAEEvAJZkYb3M2k4BUKUtyvbMjceJqmESJVsEEAAAQQQQMAnQIDok7DRu8uV9U0qjCDaqOOoKgIIRK0ADUMg2gQIEG3Yo85st5g9GUxSsWEXUmUEEEAAAQQsLUCAaOnuybly2UcQPW4Wys5ZqaB7OR8BBBBAAAEEfAIEiD4JG727HNluMfMMoo16jqoigAACCJguQIGFEiBALBRbZC9yOB3+CrjdfJOKH4MNBBBAAAEEEAiJAAFiSBjNzcTlzBpB5LuYzbWntIgIUCgCCCCAgMkCBIgmg4eiOJeLEcRQOJIHAggggAACCOQsYE6AmHPZ7C2kgNOVfQSRW8yFZOQyBBBAAAEEEMhFgAAxFxgr7+YWs5V7h7ohEFsCtBYBBKJTgADRhv3qcmV1m9vNOog27EKqjAACCCCAgKUFsiINS1eTymUXcDiyus3tCXYdxOw5s21HgRMnTsi/nx8q/QcPlv0HD9qxCdQZAQQQQMBiAlmRhsUqRnVyFzhzBJFnEHOXio0jDdq0lcQ5cyR54SK5p3lL2fnH7thoOK1EAIG8BTiKQBACBIhB4EXq0jOeQcxgBDFS/WCVcg8f/suoisN4iRw9flw69HpIb5MggAACCCBQWAECxMLKRfA6Z7ZnED18k0oEeyLsRedbwHc//iTHT540zsuQC84/33gX2XvwgKSlpeltEgQQQAABBAojQIBYGLUIX+NyZnWbmwAxwr0R2eLVc4eqBg6HQ0aPGK42JTU1VRYtXaq3SRBAAAEErChg/TplRRrWrys1zBRwubKtg+jmFnMmS0y+OTL/WKhQtpzcd3c9/yjim+PGx6QHjUYAAQQQCI0AAWJoHE3NxeHwPm+mCnV7WOZGOcTia/+hQ7Jn7z7d9JOn1G1mkVtuvEF/3rJtmxw5elRvk4RHgFwRQACBaBYgQLRh72YfQXQzgmjDHgxNlZskdJYT+vlDkasqVdSZjjFuMzuNUcW0tHRJnDtP7yNBAAEEEECgoAIxHCAWlMo657ucWbeYMzJY5sY6PWNeTVI++UT27POOHta6vYbMHD9OF16qZElp3KCB3p48fYZkZDDCrDFIEEAAAQQKJECAWCAua5zsdGV1m9tNgGiNXjGvFtt27JLHn3nWKDBDrr3qKpn27lhjO+unW4f2+sO2nTvls1Wr9TYJAjElQGMRQCBogaxII+isyMAsAdcZASKTVMxyt0o5XXv3lpMnT4nD6ZAxL4+QIq6sEWVVx1q3V5cqRuCotifPmKHeeCGAAAIIIFAgAQLEAnFZ42SnZE1SidJ1EK0BbcFafLFmjWzdsUPXrHb1GnJdlSp6++ykR8cEvWvZ5yvlj7179DYJAggggAACgQo4Az2R86wj4HRljRgxScU6/RLumsyaP1+69e2ni3E6nfLm8Jf0dk5Jm2ZN5cILL9DPIE76cHpOp7APAQQQiIAARdpFgADRLj2VrZ4uZ7YAkYWys8lE5+bW7TulQZu28q9nnpPUVO83pNStVUtKlyqZa4NLFC8u7Zo308enzEoyrkvV2yQIIIAAAggEIuAM5CTOsZaAy5XVbRmsg2itzglxbdQyNm169pCNmzbrnK+qWFHmT/1APhg7Rn/OK+nZqZM+fOzYcZmzaLHeDkVCHggggAAC0S+QFWlEf1ujpoVnjiAySSVqOvashuzeu1cat+8o+w8c1Eeq31pVlsxKlKo33qg/55dULF9e6tSqqU+bNJ3bzBqCBAEEEEAgN4Ez9jvP+MQHWwg4s40gssyNLbqswJVUI4eNO3SSLTu262t7G6OIyZMmStGiRfXnQJPuCR30qT/9ul7W/fiT3iZBAAEEEEAgPwECxPyELHjc6cg+i5kRRAt2UVBV8o0cHjp8WOejRg4H9uurtwua3FevnpQtc7m+bDKjiNohqhMahwACCIRIgAAxRJBmZuNyZZukwlftmUkf9rLOHDnMkK4d2okaOSxswU6nUx4w8lDXz1v8kfx5+C+1yQsBBBBAAIE8BZx5HuWg2QIBlaf+0fed6I6xWcz7DxySPgMHSd9Bg2XfgQM+hqh4/+vIEWnaqYtkHzkcNmhQ0G3r2Lq1FCtWTNKNPyamJSUFnR8ZIIAAAghEvwABog37WAWIDof3NnMsfdeuuvV6d/MWokbC5i5aJLUax8vbEydLWpp36RcbdqW/yof+PCx1mjaX37dsMfYFP3JoZOL/ufSSi6Vpo4b68weJs4TF1TUFCQImC1AcAvYSIEC0V3/5a+t0eLsuVkYQVXB4b8s2cuzEcb9Belq6jBg1Suo1ayGzFyzUi0L7D9poY9PWbdK0c2f568hRXeu776wtoRg51JllJt0TvN+sor5VZclnn2XujY039QdEcsqiqPhDIjZ6jFYigIAVBLxRhhVqQh0KJOB0ebsuFr5JxfdcnnpXSNVuuVlGjRgulSpUUB9l15498tiQZyQ+oVNYZ+rqwkKcfL1unTTv2lV2/rFbnE6HDOzfVz4Y+1aISxG59aYb5abrr9P5Tp6RqN9jIdl/4JDUb9VG+j89WC80Hgttpo0IIIBAKAS8UUYociIPUwVcTu9EFY+n4LOYN27aIv969lnZvnOXqXUuTGHbd+7Qgd+hw4eNyzPk5huul7nvT5ZWjeNkWXKSPP/kk3LJxRcZ1AeXGwAAEABJREFUx0R+3rBBWnR9QB56/AnZtnOn3mflJGn+Aunw0D/l6NFjcsH5JWTymNHSu0ePsFW5R8eOOu+VX66xhY+ubCGTvfv2S5dHHpWa99/vb+uatWsLmRuXIYBAlAvQvBwECBBzQAnHLjWS0X/wEPn380Pl/cREeeK552X/wYOFLsrlcuhr3W6Pfg8kUf9odvrnI9KofQeZNW+B1GnaTBq2bS9PvzRMBr04TA4cOhRINqae067XP2Tztm1Gmd7n8hZOm2pse3+KFCkiPTt3lJUL5kuPTgmiPqsjHy1fLve0aCkJRvC1ZfsOtctyr5dHj5HHn3lW0tPT5fLSpWXelA9E3VqWMP7XIu5+ufSSi3UJE6ZO0+/RlvyyYaN069NPasfHy4rVqyXdnfUHVOUrvSPO0dZm2oMAAgiEQ4AAMRyqOeTZrHNnSV6YIolz5siQ4SNl5tx5ckejOOn8cG/5Y/fuHK7Ie5fT5dInBHqLWT3D16BNG1m5Zo243en6WpVs+P13Ud/VOzUpSWrdHy/jpkw1jmf9o6rOidRr644dsnvvPl38bVWr5vpc3kV/+5u88NRTsnLhPGkeF6fPdxuB86qvvxY1qSXhHw/LpOkzZM9+b176hAgle4yRrcbtE+St8RN0Da6vcq2kfDhVqlx1lf4czkTNZE5o1VIXMT15jpw8dUpv2znZtHWrvn3cZ8BAqR0XL3EdOsjylSslPd37O1yhXFl57/X/ytrly2TGuPfs3FTqjgACCJgqQIBoEneF8uXOKcltjG58/uWXUq9FK5k1f/45x/Pa4bvFHOgs5mZdHpAjxq1MlecVZcrI2Fdelnf/+6r06Jggl/3972q3pKalytBXX9Ojil8YgaTeGcFk6qwko/QM4yVGfUfo97wStSD0mJHDZcG0KVKmVCn/qau++kqeHfmy3NEwTiIVLKp+mjZ7ttRp0kx+/u03Xbf6detI8vuTpORll+nPZiTdEjqIw+HQweGseQX7nTOjfoGWccoIbseMGy/3tW0nagLKvI8+1s+i+q4vXfIyef+tMfLFwgVy/733SMlLL/Ed4h0BBBBAIAABZwDnmHFK1Jcxc/w4qVDOGyRWKF9ej2pUMEY3VMNTU1P1A/Td+/WT/QGu7efyT1LJ/xbzV9+uk337vWsGqpG4NR8t0sueNK5fX14Y8JSsW/aJvDliuL7VqeqjllrpaNyKVs/y7SrE6KbKI9iXGt2aMnOmzqZd82b+bwPRO/JJbrnhBvl6yUeyKmWhPPvvJ+SO26r5r8geLLbu0UseGzJE1nwb3mfTlGfr7j1k4NCXdBAuDpE6NWvKxDdHyfklivvrZsaGCqIb1K2ri1KjqnrDRon6o+qDxJlSp1lzeWXMW+LOHCksXbKUdDNGD8e+MlK+/eRj+eaTJXLPXXfaqGVUFQEEELCWgNNa1Ynu2rgzb+1meDx6VEONbqhn6q6uVFE3fNmKldKgTVs9IqJ35JE4HN6ucwcwSeVfzz1r5GSMxBkjR/979T/G9rk/LRvHyWfz5kifB3vpRZXVGepZvruN0c3/vDVWjzipfWa91Ojh8RMndXFd2rXT7wVNype9Qh7s0llmTRifY7D4zbp1MntBirTr9aDccve90q1PX3n9nXfl0y9WGaOtRwta3Dnnq8BfBTGN2nWQb7//QR+/7ZabZdnsJJn27tvicBiRot5rbqJGEVWJGzdvltXffKM2bfFKWbpUGrRuK4OHj/D/wXPt1VfLf198wQgIP5IXBw0w/vBpJKVKlrRFe2KnkrQUAQTsKOCNMuxYcxvW+cpy5XWt9+zbJ8eOHdfbalbuxzMTpXfPHuJyueTwX0f0M1UqWDmQxyQWl9PbdepZO51RLslnq1b7ZyvXqn6blC6V+z+eJYoXl6f6PCqfzU02Ath7dY4qyBn93ji5p3krmbv4I73PjGTKzFm6mHq1a0m1m2/S28EkOQWL2W9DH/7rL1m+8gsdID7waB+5qe7dogK7foMGy1MvvCjzP/pIfvp1vezet1eUSX51Uc8/quVV1G3Q9PR0ufiii2Tks0MkefIkuaZy5fwuD+txZVrRGMVWhUyenqjeLP365rvvRH3DzMNPPJk5YUnkitJl5NUXnpePZ86Qts2aWbr+VA4BBBCwo4A3yrBjzW1Y59eHvahHjVTAkJyS4m9B0aJFZWC/vjLvg/fl6szRRBWs1G/dJtfRRJfTpa/35DGCqMoZPGy4Pk8FhmoZFf0hn6TcFVcYt8Bfk8Rx7xn1qSTqdBUY9R04SC8j80vmM3Rqfzhe8xYv9gcCXdq1DXkRvmBR3YZeMmumTHjzDen70INSp1ZNvdyMr8D1GzfKnEWLZHpysjw6YJDEd+wkNRs1lmvuqCU31q2nF+hu2a279Or/uAwY+qKomcljxk+QVsY+NYN6+65dOis1OvvpnNnSqXVr3f96ZwQTh8MhvoWzFy9bFvBjDWZXWU2g6t63n7Tu3lN++OUXXbwKtJ9+7DFZMX+OtG/RXJxO/hemYUgQQACBEAvwf9cQg+aVXbnLL/cvZfJ+4sxzTs0+muhwOPyjiWpm5tbtO88435m5zI3HY9w6PuNI1oe3J04SX5AydOAAUSOEWUfz36p1e3X5JGmmqBnCaqawumLdjz9JXPsEadvzQdmTOcNY7Q/la+qs2Tq7/7vmGomrX1/C+d//XXO13Fevnjz5aG+Z9s7b8uuqL2TR9GkyfPDTemRKBSQ5la/WLlSzrNcat47VN5N8ODtZz0x+ZfQY/+3kCuXKytS339bPd/omAuWUVyT2dWjZQv8+eDweyel3MRJ18pX5x9498tiQZ+R+4/ds2ecr9e7ixuj2Iz26yeqUhfJw9wfkvPPO0/tJEEAgKAEuRiBXAQLEXGnCc6BTm9Y6YzU68t1PP+vt7Il/NHHK+3JVRe+zib9s2Cj1mjfXs4sHvviSXrPQkeHQl+X2DOLPGzbIG+++p8+5q2ZNiW/QQG8XNHEZt73VGoMr5s2Vzm3b+C//au1aqdU4XvoMfFrfmnW7vcuK+E8o5MbSFSv9z8V1aZdVXiGzK9RlN153naiRS/Vs248rPhXV9pUL58tcY4RXTSxRtzYHPdZf/vFAV2nTtKncW+cuueWGG6S8MfJatEhRXWbVm26U5cmzpW7tmvqz1ZILL7xAWsXH62pNM4Lb9BD1n86wkMn2nTul/YMPSZ0mzUV9daIKXtUIoQpmP58/Vwb17y+q3oXMnssQQAABBAogQIBYAKxQnNronnv8D9FPS1LLuOSca9Ubb5QlsxKlXu3a/hNUUDktabaoNQt37v5D71fLfeiNbIlaMqdl126Slp4mTmMkcvjgQdmOFm7z75deIiOGDJbFidOlfNmyOhP1D7i6Hayel6zRKE5GjHpTNm1Vi1rrwwVO1FfpPfn88/o6FSirIE1/iHBS6coKcmW5cvpZyAb16upbm4907yZD/vW4vP7SUP0NKGppnVWLFsqmb9bI2mWfyPwpH/gn+4S1+kFk3qtLJ321mjmfsmSJ3o5UstAov36rtvLlN9+KejRC1eP+e++VZclJ8p/nnztj2SJ1jBcCCCCAQHgFCBDD63tO7mpExLdY8eyFKXLi5KlzzvHtUEHSlLffku8/Xe5fs7BU5gxN343lj5d/Kj36PSaJc+fqBa/jEjrqJXNOp6aKGIOMDYzbp5WvvFJC9d8N114rq1IWyPI5s0Xd8vNN9FATatQt7XtbtpL4hE66DgcOHQy4WBUc9ujb3/9tLmpiisvpCvh6K51YMnNdSSvVKae6qMW5a1Srpg9NitBklSNHj+rnOx95coCodThVZSqWr6BHa997/TX/KLrazwsBBBCIJYFIt5UAMQI9oG4zOxwOUbNhkwJYIPvSSy4W35qFao03tQBw8eLeZ7DUrcGlK1bIv597QX9l3i/rN+gWqdvTahRr/KjX9edQJ1dXqqRv+X25OEUvSKy+wUQFtKqcn9av1wt/V2/QSE/YePN/4/Qkg4wMX1irzsp67fxjl7Tt0ct/a1mtZ6eWphH+C7tA94T2ugw1U/ib777X22YlajH2+9q00zPEVZlqlDZ58kT5fMFcPVqr9vFCAAEEEIiMAAFiBNzzm6ySX5XUAsCVK3hHBUvk8LB+jWq36tvT6jZ1fnkFe9zlcukFiceMHC7fLVuqb0OrZ/FUviogVOv/vTp2rF6mpFr9BvLEs8/Jy6NHy2tvv2OMfPaX2xs2kjvjm4kKKtU1armfFwcNUJu8TBBofN99erKKKurpYcPUW9hfp0+fludeeUU6Pdxb1JJPqkA1w3tJ0kypXrWq+hglL5qBAAII2FeAADFCfadGEVXR6rnCnCarqGN5vZwu7+3XurVry/rVq854JU2cIL7RvLzyCPWxv/3tQj2RRT2Lt3bpEr1OXbwRgKj9qqxDfx6WmfPmy1vjJ8qod/8nS1d8nrngsXEv3Dihft26erkfY5MfkwSKGL9HtWvcrkvbsm2bqOBNfwhT8rMxuqzWl5w4bbqoPyDU7G41Iq7WiCzoLPswVZFsEUAAAQQMAQJEAyG3n3DuD3SySm51cDm9XefOcOuva1Nf2eZ75XaNmftLXnaZnszxzquvyA+fLpekiePl0V49pezll+tq/P3SS6VF3P16okfiOCNYTJ4tk0aP0sdIzBV4qm8fXeDp1DT5+NNP9XaoEzXLfdT/3pNmnbvKlu3bdfZqeSH1rTJqRFzvIEEAAQQQsIyAN8qwTHVipyIFmaySk4rL5e06j9uT02FL7XMZo1Q1qlWTAUYgop5Z3P7dWvlu+VIZPXKEXipGrbdYpXIlS9U5liqjJh6pCSuqzWrilHoP5Uutxdnyge7y2ti3RT0zq5aqUUsIqQXK1fO1oSyLvBAIUIDTEEAgHwFvlJHPSRwOj4C6zexwBD5ZJXstHL4RRAusX5e9XmzbU6BN0ya64p9+sUr+OnJEb4cieX9GojRs006+//lnnV3N6rfJkpmJehFyvYMEAQQQQMCSAgSIEeyWYCarqPUNVdXTbTCCqOoZ8hcZhlSgVdN4cTgc4jb+4Ji7aHHQee87cEAv7D5kxEg5eeqUFClSRAY//pgkjntPyl1xRdD5kwECCCCAQHgFCBDD65tv7moUUZ2kJqusXPOV2gzopb7mTZ24cdPv6o0XAkEJXFG6jNSodqvOIzllkX4vbKImIzVq117U77TKQ93C/njmDPlntwd0EKr28UIAAQRyE2C/NQQIECPcD2qySokSJXQthr72mn4PJCldspQ+rVTmu/5AgkAQAq2bxOurv/3+e9m9b6/eLmjy26ZN0qRjJ1FBorpWfROQ+paZaypXVh95IYAAAgjYRIAAMcId5XQ6pV7tWroWv2/eKuqbJfSHfJKyZcroM3zv+gMJAkEINGnYUN8KVlnMnDNfvRXo9dmq1dKi6wOya88eUROT1NI16puA1O3lAmXEyQgggAACERcgQIx4F4gMf3qQqPXo0tPTZMacuRaoEU6ihTkAAAd8SURBVFWIRYGLL7pIGtStq5uuvrpRbwSYTPxwunTv20+Onzgpat3Lqe+MFbX4dYCXcxoCCCCAgMUEcgwQLVbHqK9OqZIlJa5BA93O8VOm6QWE9QcSBEwWaNWksS5RLU3z4y+/6u28Eo/HIwOHviTPvfyKnuCivi5PfcXjnTVq5HUZxxBAAAEELC5AgGiRDuqe0EHX5I+9e2T5yi/0NgkCZguoZ2IvON/7TGxySkqexavRwm59+sq02bP1edVuvkkWfjhV1PeA6x0kVhSgTggggEBAAgSIATGF/6Q7bqsmvsWK309MDH+BlIBADgLqecGmjRrpI8kpi3Idzd61Z48079JV1HOH6uTmcXEya8J4Ubep1WdeCCCAAAL2FiBAtFD/9ercUddGjSCqkUT94eyEzwiEWaBVvPc288FDh2TpipXnlLbux5/0TOWNmzfrZWuefLS3jBk5XIoWLXrOuexAAAEEELCnAAGihfqtVZMmor6GLCMjQ9SziBaqGlWJIYHaNWpIieLe28xnL700b/Fiaduzl17G5rzzzpN3XvuP9H3owRjSoakIhE+AnBGwkgABooV6o0Tx4pLQsqWu0YfJyZKamqq3SRAwU8DhcEj9unfpIrdu3y6Lly3T26+/8670Gfi0pKWlScnLLpPZEydI4/r19TESBBBAAIHoEiBAtFh/dkvooG/bHTt2XGYtWGCx2lGdvAWi5+jokSP8z8T2e3qIxLVPEBUgqhZeX+VaSflwqtx8w/XqIy8EEEAAgSgUIEC0WKdWLF9e7rnrTl2rvG4ze4zb0PokEgTCIKDW5Rzz8nDjjxWnnDp1Sn757TddSv26dWT25IlyeenS+jMJAgggEBMCMdhIAkQLdnq39h10rdQkgK/XrdPbZye/b9msd23aulW/kyAQagGHOKRY0SL+bK+rUkUmjHpDfMvg+A+wgQACCCAQdQLOqGtRFDTo3rp3Sdkyl+uWTJqe85I3p057n0/kH2vNRBJigWWfr5QWXbvJ6dRUI0z0Zr591045eOiw94P9UmqMAAIIIFAAAQLEAmCZdarD4ZCemUveLPrkE9l/4MA5RZ84eULva9KwoX4nQSBUAm+NnyA9+vWXk8atZbWu4X+HDRWHwyEnTpyUDsxYDhUz+SCAAAKWFrBPgGhpxtBXrlPr1lKsWDFJd7tlyqykMwo4eOhPUZNY1M7KFa9Ub7wQCFrgz8NHpEnHzvLy6DF6geyrK1WSRdM/lDZNmsqFF5yv899/4KB+J0EAAQQQiG4BAkSL9q9aD7F1k3hdOxUgqkBRfzCSrTu2G6n3p2KFCt4NUgQKKbDPGKH+xxNPyu0N75Mff/1V56ImSs2fOkXKl73CGDk8ISczH2lwezz6OAkCoRQgLwQQsJ4AAaL1+sRfo4e6dtHb+41/wNWtZv3BSLZu32Gk3p8qlSt7N0gRKKSAGjVcvHSppKWl6xwuveQSPUt52OtvyIw5c6R6w/slPS1NHyNBAAEEEIgNAQJEC/ez+m7m22+9Vdcw+2SVnzes1/vUYsXqNrT+ENGEwu0scPyE93lWXxv+PHxYpifPkamzZsmTzw+V48eP+w7Jzddf599mAwEEEEAgegUIEC3et90T2usaquVu1n7/g95evHS5flffaKE3SBAIQiDQoO/2qlVlxrj3giiJSxFAwHYCVDhmBQgQLd718Q0bSrFi5+laPvLUAFn19deyc/du/bn6rbfodxIEghFQQd/a5cskp9f61av8+9UC2cGUw7UIIIAAAvYRIEC0eF+pb7S4585aupa79+6Vro88amxniNo/6qWXjG1+EMhTIKCDJS+9RHJ6nV+iuH9/QBlxEgIIIIBAVAg4o6IVUd6IcW+8Lr179tCtTEtXEwkcUrx4cVFr1OmdJAgggAACCCAQYwLhbS4BYnh9Q5b7wH59pUY174QVEQeTBYT/EEAAAQQQQCBcAgSI4ZINQ75JEyfIsjmzZe3ypUwWCIMvWSJgtgDlIYAAAlYVIEC0as/kUq9rKlXSz4TlcpjdCCCAAAIIIIBA0AIEiEERcjECCCCAAAIIIBB9AgSI0dentAgBBBBAIFgBrkcgxgUIEGP8F4DmI4AAAggggAACZwsQIJ4twudoEaAdCCCAAAIIIFBIAQLEQsJxGQIIIIAAAghEQoAyzRAgQDRDmTIQQAABBBBAAAEbCRAg2qizqCoC0SJAOxBAAAEErC1AgGjt/qF2CCCAAAIIIICA6QKFDBBNrycFIoAAAggggAACCJgkQIBoEjTFIIAAArYQoJIIIICAIUCAaCDwgwACCCCAAAIIIJAlQICYZREtW7QDAQQQQAABBBAISoAAMSg+LkYAAQQQQMAsAcpBwDwBAkTzrCkJAQQQQAABBBCwhQABoi26iUpGiwDtQAABBBBAwA4CBIh26CXqiAACCCCAAAJWFoi6uhEgRl2X0iAEEEAAAQQQQCA4AQLE4Py4GgEEokWAdiCAAAII+AUIEP0UbCCAAAIIIIAAAggogWgKEFV7eCGAAAIIIIAAAggEKUCAGCQglyOAAAIIhFuA/BFAwGyB/wcAAP//awQfggAAAAZJREFUAwCdG0HaZl9bCAAAAABJRU5ErkJggg==</t>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Trichy</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>wefwsf</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>wefwef</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAogAAAC2CAYAAABapnxOAAAQAElEQVR4AezdCZxP9f7H8feMbZbQYh+qe11ab3WLm4hsCRn7vhOyxI2iJFtlSZKQneyMJfsSUiRtqG5/KqIsQ7ayjrEM//l+ZzF1LcPM7/c75/d79ZjzPfs53+/z+3s8+jjnfL/f4Itnj19kwoDfAL8BfgP8BvgN8BvgN8BvIOk3ECz+QwABBBDwQwGKhAACCNy4AAHijdtxJgIIIIAAAggg4JcCBIgOrlayhgACCCCAAAII+EKAANEX6twTAQQQQCCQBSg7Ao4XIEB0fBWRQQQQQAABBBBAwLsCBIje9eZu/iJAORBAAAEEEPBjAQJEP65cioYAAggggAAC1yfA0QkCBIgJDqQIIIAAAggggAACiQIEiIkQzBBAwF8EKAcCCCCAQFoFCBDTKsj5CCCAAAIIIICAnwk4MkD0M2OKgwACCCCAAAIIuEqAANFV1UVmEUAAAVcLkHkEEHCJAAGiSyqKbCKAAAIIIIAAAt4SIED0lrS/3IdyIIAAAggggIDfCxAg+n0VU0AEEEAAAQSuLcARCKQUIEBMqcEyAggggAACCCCAgAgQ+REg4DcCFAQBBBBAAIH0ESBATB9HroIAAggggAACCHhGwAdXJUD0ATq3RAABBBBAAAEEnCxAgOjk2iFvCCDgLwKUAwEEEHCVAAGiq6qLzCKAAAIIIIAAAp4XIEBMrTHHIYAAAggggAACASJAgBggFU0xEUAAAQQuL8BWBBD4XwECxP81+dOWX3btUudXe2n33n1/2s4KAggggAACCCDgrwIEiJep2VOnTunl1/upcbv2KlO9puYtWaIyNWqodZcu+nnnL5c5g02+FeDuCCCAAAIIIJCeAgSIf9E8ceKkij8dqRnz5mnd51/owoWL9ohz587pwzWfqGHbtnadBAEEEEAAAQQ8LMDlfSZAgJiC3gSH9dq00R9Hj9qt+fLkUffnO2nskLd1e/78dtux4yfsnAQBBBBAAAEEEPBXAQLExJo9efKU6rZqrf/74Ue7pVZkFX2+fKnatWiuimXL6IX27ez207Gx2r5zp10mQQCBawpwAAIIIICACwUIEOMrzQSHdZ5ppS0//RS/JpngcMhrfRUUFGTXTfL4v4uamZ0+/3qjnZMggAACCCCAAAL+KHDtANEfS52iTKkJDs3hOXPk0J0FCphFfb5xk52TIIAAAggggAAC/igQ0AFiaoPDpIp/rGgRu7j+yy/tnAQBBBBwswB5RwABBK4kELAB4vUGhwawWJGEAPHY8eN8h2hAmBBAAAEEEEDALwUCMkC8keDQ1L7zvkM0uWJCAAEEEEAAAQTSVyDgAsQbDQ4NO98hGgUmBBBAAAGPC3ADBHwsEFABYlqCw6R64jvEJAnmCCCAAAIIIOCvAgETIO7Zu0/la9e+alc2qalkvkNMjRLHSAIBAQQQQAAB1woETIBYp1Ur7fvtgK2ohrVq6a/9HNodqUj4DjEVSByCAAIIIICA3woERsECIkDc8euu+ODwN1ujjzzwgAa8+sqfOsG2O1KZ8B1iKqE4DAEEEEAAAQRcKxAQAeKE6dNtBWXOnFnvDx92w8GhvUh8wneI8Qj8IeBiAbKOAAIIIHB1Ab8PEI8eO655i5dYhVpVntbN2bPZ5bQkfIeYFj3ORQABBBBAAAGnC7g0QEw964x583Q6Ntae0KZpEztPa8J3iGkV5HwEEEAAAQQQcLKAXweI5+PiNG5awuvlko89qoJ33pkudcF3iOnCyEUQQACB/xVgCwIIOELArwPEpatW68jvv1voVo0a23l6JXyHmF6SXAcBBBBAAAEEnCbg1wHiqInvW+/bIyJUukRxu5xeCd8hXlGSHQgggAACCCDgcgG/DRA3fvuttm7bZqunbfNmaW65bC+UIkn5HeLKj9em2MMiAggggAAC/ihAmQJJwG8DxPHTZth6NK2Wa0VWscvpmZjvEMNCQ+0lZ3zwgZ2TIIAAAggggAAC/iDglwHi/oMHtGLNGls/ZtSU0JAQu5zeSYH4V9f2mhcv2hkJAk4XIH8IIIAAAgikRsAvA8TxU6frwoULypghg1o3bpQahxs6pnL5cva8mMRudOwKCQIIIIAAAggg4F2BdL+b3wWIps/DmYmvfKtUeFK33XpruqMlXTAib167aFpKn4o5bZdJEEAAAQQQQAABtwv4XYA464MFOnkqxtZL2xbN7dxTSf58CQGiuX70/n1mxoQAAgjcmABnIYAAAg4S8KsA8eLFi5owPaFj7CIPPaR7Cxf2KHWBfBHJ198bvT95mQUEEEAAAQQQQMDNAn4VIK5au1a7o6NtfbRq4rlvD+0N4pOIvHni04S/vb/tS1ggRcABAlt+/FEvvfa6nu/RUy/26avOr/bUbwcPOiBnZAEBBBBAwA0CfhUgjk8cVi9vrtyqWKaMx/2Dg4OVP/E18959vGL2ODg3uKzA8RMn9MlnG/TO6DFq9lxHPfBEGVWq31AzP5ivD5Yu1ewFCzVvyVKVeDpScxcvvuw12IgAAlcTYB8CgSfgNwGi6RT7i42bbA2ap4cmeLMrHk6SurrZwytmD0tz+SSBX3bvUueevWSeClaoU0/3l3xCTTs8ZwPEj9d/pqPHjiUd+qf5uXPn1KVnbzXv1EmHDh/+0z5WEEAAAQQQSCngNwHiuKnTbLlMn4cNata0y95IIvIkNFShkYo3tG/8Hv5w5paffrKvjZ+oWkPzFi+xTwV/3L49uWjhYaF6vNij6ti6lSYOG6oNy5dq88dr7DTv/YkqeOcd9tg169arXK3amr9suV0nQQABBBBA4K8CfhEgmm5mFib+z65+zeq6KTzsr+X02HqBiHz22nv27bdzEgTSWyAq/hVxZKMmqlSvgX1trMR+2W+95RbVjoxU/x6vaPmsGfphw2eaMXqUunZor/KlSil/3rzKccvNdir6r4e0cs5stW/ZQhkyZIh/ynhc/3mlh30lffjIkfTOMtdDAAEEvCXAfTwk4BcB4qRZUTofF6egoCA908jzjVNS1kVE/P+EzboJUukL0Uhce4qJiVH3fgM0dPQYmdee1z4j8I7YHR2tfu8M1YOly6hrn776bssWixAWGqKGtWoqatwYffvxRxryel81rlNb9919t91/tSRTpkx6uVNHLZo6JflponklXbZmLZ4mXg2OfQgggEAACrg+QDx79qwmR0XZqnvyiSd0e9Lwd3aL55OkRirmTrxmNgrXnkpGVtP0OXM0JD5AfLqBdwP6a+fOd0eY0X9Wr1tnvycsWaWqxkyeoj+OHrMZKnjnnerbrZs2rlqlgb1e1WNFi9rtN5L88957kp8mBgUFJT9NNN8mHj12/EYumbZzOBsBBBBAwHECwY7L0XVmyLTOTPqfWisPDqt3pWwVoC/EK9FccfuZM2eS9wUHZ0heDtSF3/84qvcmTLStjFt2et62SDZ9epqhIiuXK6dZY0fr4wUfqEXD+rrppvB0YUp+mjhtiv5+x6VvE/sPHZou1+ciCCCAAALuFkiPANGnAmOnTLX3N51iFyvyiF32ZhJBX4jXzV24YMHkc54qWzp5OdAWNn77rTp1f0VFKzylN4ePUPT+/ZYgd86c6tz2WX354XKNfvstFf/3v+12TyQP3nefVs2drXYtmttPNB64915P3IZrIoAAAgi4TMDVAeLiFSu149dfLXnrJo3t3NtJMH0hXjf5oN69ks/Jny9f8nIgLMScjtX0ufP0VJ36qtm8pRYsX5H8HaYJBE1A+PmKZTZAzJkjh1dIzNPE7v/ppF3fbLLfM3rlptzEJQJkEwEEAlXA1QHiwOHDbb1lyZxF1SpVtMu+SAokfve4h74QU8cfdOmw/PkSugm6tMU/l3b8uks9B7ypIk8+qe5v9NMP27fZgmbNepN9dbx20QL7Ktm8Ujavlu1OEgQQQAABBHwk4OoAMXPmjJbt7sKFlDFjwrLd4OXEyX0hepkiVbfbE70v+bgCKb7hTN7oJwvnz5/XkpUrVbdVa5WpXsM2pjp58pQt3X133WUbm2xatdI2Pvnb7bfb7SQIIIAAAgg4QcDVAeLN2bJbw0J/+5ud+yopEJHwmpS+EFNXA0nDEponZXly50rdSS466sChQ3p75Cg9WrGy2nd7WUkj/GTOnFk1n66s+ZMnaXnUTDWsWVMhISEuKhlZRQABBwmQFQQ8KuDqADGp38HwsDCPIl3r4hH0hXgtoj/t/2X3brueK0cOmSDRrvhBsv6LL9Wmy4sqFh8Yvjt2XPJwduYfEOYbv43xTwuH9ntDjzz4gB+UliIggAACCPizgKsDRNPhsqkc03mwmftqyp/iO7ro/Zden/oqP06/77LVH9ksnr9wwc7dnBw8fDj+KeFLMv0WNmzbTivWrFFcXJwtUtmSj2vSsGH6bOkS20r45uzZ7PbkhAUEEEAAAQQcKuDqAPHU6dOWNczHTxALpPiObi8NVWydXClZ8+l67fvtN7u7yEPufZJmhqd7/e0hevSpSlqycpV27d1ry5Q9WzYbDG5YtlSThg9T2VKP2+0kCCCAAAKBI+APJXV1gHj6dIytA9+/Ys5j82GSvb/xBNE4XG4ynwR0f72f3WVeuw7rl7BsN7gkMQ1sXo4vw8PlntS4qdOSnxbmj3+K/G7/fvp+3Scyr5PNukuKRDYRQAABBBD4HwHXBohmpAnTp5wpka9fMafsC3F3dLTJEtNlBAaNGK79Bw/YPW/37SvTaMOuuCD5cft2dXy5u0pVraYZ8+Yl57h0ieKaM2G8zBPDGpUrJW9nwe0C5B8BBBAIbAHXBojmaVRS1YWFpc/wY0nXS8t85cefpOV0vz33/374UZNmRtny1ateTb4Y9cbe/DqTzf/9Xs07dVKFOvW0cMWH9omh+QdBlQoVtHJOlKa8N0KPPvLwdV6VwxFAAAEEEHC2gGsDxKTXy4b3ck8QzXZvTiFZQuztkp5q2hUSK2AabTz/ak+Zp7633JxdvV54wW53cvLJZxtU55lWqt60mdasWy/znxlxpH6N6vpk4XyNHDRQdxcqZDYzIYAAAggg4HcCwW4tUVIDFZP/8NBQM/PpVObxEvb+YfRrZx1SJmOnTNO2HTvspr4vvSQzeohdcVhy4cIFLVm5UpXqN1TTDs/py02bbQ7NP0BaNW6kz5ctlRkm8M4CBex2EgQQ8IkAN0UAAS8IuDdAjElooGKMnPCKOedtOUxWdPDwITsnSRDYE71P74wZY1fMa+XqPhwS0WbiMokZ8WTW/AUqU72m2nd7WVt+/NEeZVokP/9sG32xYoV6vfiCcuVMqGO7kwQBBBBAAAE/Fgh2a9lOJ3ZxY/JvnvCYuS+npODBvGJO+X2kL/PkhHu/0Lu3YmNj7YghpmGKzZNDEpOv8dOmq3jlKurW9zUldeCdO2dOvdqls778cIW6tGsr+i90SIWRDQQQQAABrwm4NkBMGYSFO6CRSq7bbkuutENHDicvB/LC/GXLk4eZ69K2rUzXNk7wOH7ihIaOBvt90AAAEABJREFUGatHK1bSa4Pf1m8HD9ps3ZE/vwb27KHPli5Wm6ZN5IR/eNiMkSCAAAIuESCb/iPg2gAxJjahk2xTFaEO+O4v6Qmiyc/BQwSIJ06cVJ9BgwyHChcsqNZNGtllXyamc+t+7wzVo09V1JBRo/XH0WM2O/cUKqzhAwdo7aIFalirlqu637EFIEEAAQQQQCCdBdwbIJ669A1ieLjvG6nkTPwG0dQPTxClvoMH2wAsKChIQ994XRkyZDA0PpnMd5Cmc+tilZ7WmMlTlPT0uchDD8kMhffhnFmqVvEpme5rfJJBR92UzCCAAAIIICC5N0BM/AbRBB5JXcz4skJN9y0ZM2a0WTh4+IidB2ryxcZNmr1wkS1+i4b1df89d9tlbyd/7dz67NmzNgulSxS3nVt/MGkiQ+FZERIEEEAAAb8XuM4CujZATHoKFBoacp1F9tzhuRKfIh48HLivmE0QZhqmGOW8uXLr5Y4dzaJXJzq39io3N0MAAQQQ8EMB1waIMUnjMIeGOaZacuZIaKhyKIADxGHjx8u80jWV8lbf3rb1sln2xkTn1t5Q5h4+FODWCCCAgNcEXBwgJjRSCXNAJ9lJtZUzsSXzwQANEHfu2qWRE963HJXLl1epx4rZZU8mdG7tSV2ujQACCCAQqAKuDRBPJXaUHRbmnCeIuXLmtL+jQ1f6BtHu9c/EDKPXpWcvnY+LU3hYqN7o/pI8+R+dW3tSl2sjgAACCAS6gGsDxKSOsk0w4pRKzJX4ivngkSNOyZLX8jFtzlyZb//MDXt07qwciU9TzXp6Tlfq3DpXzhx0bp2e0FwLAQSuS4CDEfA3AdcGiKdinPeKOVeOhKHYTH975omav/1YrlSevfui9drgwXb3ww/8U43r1LbL6ZkcOHhIzTv+R/9+qmL8vS51bn17RITt3HrjqpV0bp2e4FwLAQQQQCCgBVwbIMbEJvSDGObARiomODRBYiD8skygXrVJM505e05BwUEa3LdPuhb7zJkzGjF+gopXqaI1n36qo8eO2+vf9Y9/aNiA/lq/dLHt3NpuTFPCyQgggAACCCCQJODeANGBTxBTdpZ9MABeM5vgrXnHjjp85Hf7eypTooT+8be/2eX0SExfiqUiq2vQiPd0Lj4ANdfMnzevJg4bqlVzZ6t6pYpmExMCCCCAAAJXFmDPDQm4NkA0T65MicMd1Egld86EV8wmX/4+3F5cXJzadu2mLzdtNsVV5XLlNPHdoXY5rYnpaPvJ2nX1Yu8+2n/wgL3c3++4Q2OHDNaG5UtVvlQpu40EAQQQQAABBDwj4NoAMSapFbODOsrOndiK2VTVIT9+gmheoT/f41V9tO5TU1Tbnc2IQQOV1qHqfv7lFzVp30F1W7XWTz//bK9926236PXuL2n1B3NVsWxZu40k4AQoMAIIIICAlwVcGyCeShxqL8xBTxDNUHvZs2WzVXjw0CE798ekR/8BWrjiQ1u0Rx58UBOGvqOMGTLY9RtJDsRbmaeF5WvV0doNn9tLhISEqGPrVvp08WI1q1cvTde3FyRBAAEEEEAAgVQLeCdATHV2Un/g6aSRVBwUIJrc57j1VjPTnuhoO/e3ZPDIkTJd2phyFS5YUFNHvqcsWbKY1eueTp6Ksd8XloysJvO9oen02jyFrFutqjYsXayuHdrrpnDn9HN53QXkBAQQQAABBFwq4MoA0bzijDkda8nDHPSK2WToVGLguuHrjWbVr6aJ02dq2Njxtkyme5mocWNuKIAznWlPjopSychI20LZ9G1oLlq6RHGtnjfHtoT2VD+K5j5MCCCQfgJcCQEE/FPAlQFiUgMVUyVhYeFm5pjpzgIFbF7Ma1PTkMOu+EEyZ9Fi9XnrLVsS863l7InjdFvi01K7MZXJijVrVL5mbfUc8KaO/P6HPct0WTN7/DhNeW9EuraCthcnQQABBBBAAIHrFnBlgJj0etmU1mlPEDu0bGmypdgzZ/T1N9/aZWcn186daYzStU9fe+AtN2dX1Pixypc7j11PbfLfrVtVrUlTtenyonbu2mVPM9d45/XXtHJOlIoVecRuI0EAAQQQQAAB3wu4MkA8ldhAxfCFh4aamWOm4kWLKDQkxOZn9bp1du7m5PONG9XmhRdlvg803wPOHDtGpsuZ1JZp7779avtiN1Vp2FjffP9/9rSsWW9S9/900tpF81UrsoqCgoLsdhIEEEAAgXQU4FIIpEHAnQFiYhc3ptxOe8WcKVMmlS5e3GRNq9e6O0D8bssWNX+uk86dO2cbopgGKfcWLmzLdq3kj6PH1HvQIJWqWk3LVq+2h5tW3i0a1tf6xYvVrkVze027gwQBBBBAAAEEHCXgygDxdIoniE57xWxqt3zpJ8zMvkrdE73PLrst2bZjhxq1ba/TsbG2ixnTlY3p0uZa5TCjq4yc+L4ej4zU+zNm6fz58/aUyuXLa92iherbrZvMa2q7keRaAuxHAAEEEEDAJwLBPrlrGm+aspFKuMMaqZiilStZMvm1qWmUYba5adodHa16rZ/V8RMnbDlMJ9ilHit21SKYluXzFi/RE1VraOCw4Tpx4qQ9/l//vF9LZkzT6MGDlD9fXruNBAEEEEAAgcAWcH7pXRkgxsSeTpZN+t4veYMDFm695WaZwMhkxW2vmQ8cOqS6LVvryO+/m+yr3yvd7TB6duUKyRcbN6lCnXrq3LOX9h34zR5lvlM0Q+MtnDpFD9x7r91GggACCCCAAALuEHBngHgqJlk3PNxZjVSSMpY0XvBX33yjkydPJW129Nx8N1ivVZvkIO+ljs+pcZ3aV8wzQ+NdkYYdASBAERFAAAF/FnBngJj4DWKGDBkUkiXEkfVT/olSNl+mL8SP1q+3y05OzLeGDdo8a7+bNPls2aiBOjyT0GWPWU85maeMDI2XUoRlBBBAAAEE/EvAlQFi0jeIoWkaRcWzFXl3oUIyHUqbu3y0dq2ZOXYyrZRNa+Wt27bZPNapGqk+Xbva5ZQJQ+Ol1GAZAQQQQAAB/xVwZYAYkzicXXios8fprVSurP3lrP70U5kniXbFYYnJl+nn0PR3aLJWuVw5vdWnt1lMnhgaL5mCBQQQcIMAeUQAgTQLuDRATGikEuawTrL/WhvlSiW8ZjbfIDpxVJWLFy/q+R6vyoyUYvJuWiqbFsvBwZd+FqYVNkPjGR0mBBBAAAEEAkfgUiTgojKfSuwoOyzM2U8QnT6qSo/+A7RwxYe25k0fhxOGvmP7PDQbfDw0nskCEwIIIIAAAgj4SMCdAWJiK+YwB3+DaOrTyaOqDB45UtPmzDXZVOGCBWVGScmSJYsYGs+SkCCAAAIIeESAi7pFwJUB4lebN1vf3Xuj7dzJiRNHVZk4faaGjR1v2W6PiFDUuDE6cfKE6rZqreKVn04eGs8c0LReXYbGMxBMCCCAAAIIBJCAKwNEM6avqaMsWTKbmaMnp42qMmfRYvV56y1rZlpZjxkyWKMnT1GJp6vIdHhtd8QnVStW1IZlS/VG95cZGi/eg79LAiwhgAACCPi/gCsDRPNK9GJ83RT+e8H41Nl/ThpVxTRG6dqnrwXLnj2rihctqmpNmmlMfIB4/nyc3X57/vx2aLwRA/szNJ4VIUEAAQQQQCAgBP5USFcGiKYEQSZxyeSEUVVMNzamO5sLFy4oU8YMOnkyRvOXLdPZs2etYsnHHtXs8eO0fskihsazIiQIIIAAAggEroBrA0Q3VVn5FKOqLFq50utZ/27LFjXr0FGmQ2xz83PxTwtN/4dBQUGqULq0ls+aoemjRqlYkUfMbiYEEHCrAPlGAAEE0kmAADGdIK92GTOqSnhip94jxiU0Drna8em5b0l8QFqjWQvFnjmTfFkzRGH1ShW1et4cjR86RPfdfXfyPhYQQAABBBBAAAECRC/9Bu6/7x57p7379+vXPXvs8mWSdNu04auvVD0+MGzf7WWdP3/eXtcEhg1q1tC6RQs1bEB/Ffr73+12EgQQQAABBBBAIKUAAWJKDQ8uj3pzYHIn1JNmzfLYnUxDlOpNm6l+m7ba/N13yfd5rGgRfbliud7s1VMFIvIlb2cBAQQQQMAbAtwDAXcJECB6qb5y3HabIp+qYO82e+EinY6NtcvpkZiGJ+ZVcsW69dWi03+0+b/f/+myHVs9o6hxY5UrZ44/bWcFAQQQQAABBBC4nAAB4uVUPLStTbOm9spmbOaoBQvtclqS83FxMsFm2Rq1ZF4lb922zV4uOOhSG+9n4+/Z9bkOdjtJ2gQ4GwEEEEAAgUARIED0Yk3fd9dd+tc/77d3HD91mi5eNL052tXrSkzXNJOjolSySlW92LuPdu7aZc/Pni2bQrJk0YXE6/774YfVo/Pzdh8JAggggAACCFxWgI2XESBAvAyKJzc1b9DAXn53dLSmz52nQ4cPy7withuvkcScjtXoSVP0WOUq6jngTUXv32/PyB+RT8UeKaJjx4/b1sqmc+5Z48Zo7kTvtpi2mSFBAAEEEEAAAdcLECB6uQojKzyp0NBQe9dX+vXXI+Ur6M6Hi+iBJ0qrTPUaqvNMKz3b5UV1f6OfBo8cqfdnztK8xUvUre9rKlaxovoPHWqDSnOBgnfeoZ4vvqDQLCH6YtNGs8mOjrJ67hw7txtIEAgEAcqIAAIIIJCuAgSI6cp57YtlzJhRFUo/oUtfCSacc/TYce34dZe+3LRZy9essU8Xh40dr95vDlLnnr00a/4CmWPM0Xf94x8aOWig2rVoobffe0/bd+60LaRf6vicZo4dLdMgxhzHhAACCCCAAAII3IiAUwLEG8m7a88ZPqC/ftm8UZtWr9TKOVEyr4NHDOyvvi91U6c2rdSodi1VKltWjz7ysMxTwvCwhCeOt0dEaPKI4Vo0bYqWrV5jvz80r53z5c6jue9PVIdnWioo6K+hp2uZyDgCCCCAAAII+EiAANFX8MHBypkjh8woK8WLFlXV+NfHLRrU14vt22vAqz00ZshgzZkwXh8vmK8fNnym3d9u1vqli5U7V05VqF1Xplsbxf9XttTjWjV3th5+4J/xa/whgAACThMgPwgg4EYBAkQX1drE6TMV2aiJdu3dqyxZsuiN7i9r0rBhypr1JheVgqwigAACCCCAgNMFCBCdXkPx+TOtk5t36qQ+b72lc+fO6Y78+bV0xjQ1rVc3fq/n/7gDAggggAACCASWAAGiw+vbjIpSrlZtrVm33ua0TtVIrYx/pVy4YEG7ToIAAggggMANCnAaAlcUIEC8Io1vd5i+EYeOGataLVrq4KHDCg0JsS2X336tr132be64OwIIIIAAAgj4swABogNr9/CRI6rzTGsNGTVacXFxurdwYfvUsEqFCg7MLVnyqQA3RwABBBBAwAMCBIgeQE3LJdd9/oXK166jr7/5xl6mZaMGWjJjmv3u0G4gQQABBBBAAAG/F/B1AQkQfV0Difc/f/68Xn97iJq076Df/ziq7Nmy2RbKfbp2lelcO/EwZnnYSvwAAAh6SURBVAgggAACCCCAgMcFCBA9TnztG+zdt19VGjbWuKnTdPHiRRX917/00by5Mn0cXvtsjkAAAWcKkCsEEEDAvQIEiD6uO9Ph9ZO1a2vrtm0KDg7W88+20ZwJ45QrZw4f54zbI4AAAggggECgChAgXqXmPbnrzJkz6tb3NbXv9rJOxZy2AaEJDLu0a2sDRU/em2sjgAACCCCAAAJXEwi+2k72eUZg244dqlivvmbNX2BvUOqxYvaVsnm1bDeQIIAAAgh4UoBrI4DANQQIEK8BlN67p8+dpyqNmmjHr7uUKVMm9Xyhi6aNGmkbpaT3vbgeAggggAACCCBwIwKuDhAv6uKNlNkn55w4cVKtO7+g7m/0U2xsrPLny6vF06eqdZPGPsmP629KARBAAAEEEEDAYwKuDBC379xpQX7+5Vc7d3ry/dYf9GTtuvrw449tVk2H16vmzrUdYNsNJAgggAACCCBgBUicIeDKANH0EWj4YmJizMyxk+myZtT7k1WtSVPtO/CbHSJvUO9edsi88LBQx+abjCGAAAIIIIBAYAu4MkCsV72arbUjf/whM2axXXFYYjq7btCmrQa8+67Ox8WpcMGCWjZrpurXqO6wnJIdBNJbgOshgAACCLhdwJUB4r13FbbuJjg0LYLtioOSDV9/bYfLM3OTrcZ1amvZzOkqeOcdZpUJAQQQQAABBBBwtMBlA0RH5zg+c/cUvis+Tfjbum17woID0oOHD6vZcx3V8Nl2OnzkiLJmvUnj3nlb/Xu8osyZMzsgh2QBAQQQQAABBBC4toArA8Sw0BDdHhFhS/fDtm127svEfGs4OSpKxStX0cfrP7OvvR+87z6tnDNbT5Up48uscW8EEEAgpQDLCCCAQKoEXBkgmpLdUzjhNbOvA0TTQrlKo8bqOeBNnT171mRNZR4vYbuwiciTx66TIIAAAggggAACbhJwbYB4b+J3iL56xXzy5Cn16D9AkY2byASJptIffeRhfbpkkSaPGG5WPTNxVQQQQAABBBBAwMMCrg0Q7ylcyNKYb/2OHT9ul72VzFu8RCWrVtPU2XPs6+RcOXNoxMD+mjNhvO7In99b2eA+CCCAAAJ+JEBREHCSgIsDxIRXzAbzv1t+MDOPT2Z4vBrNWqhzz1468vvvypAhg1o2aqC1CxeqasWKHr8/N0AAAQQQQAABBLwh4NoA0TypM41VDNIP2z3bUOV0bKz6vTNUT9aqrU3ffWduqYfuv0/LZk1Xn65dRafXloREECCAAAIIIOAfAq4NEA1/UkOVrR5sybzso49UumoNjZk8xXZ4fcvN2WVGQ1k4dYruKXTpKabJDxMCCCCAAAII+KFAABbJLwLEHz3QF+LefftVv01btX2hq/YfPKCgoCA1qFlDny5eZEdDCQoKCsCfC0VGAAEEEEAAgUAQcHeAWCihocqPP/9sG4ukR4WZrmreGT1GZWrU1IavvrKXNE8KzRPDN3v1VLasWe02EgQQcJUAmUUAAQQQuA4BVweISV3dpNeQeyYgLF29hkyAeObMGd10U7j6duum5VEzZL45vA5XDkUAAQQQQAABBFwr4J4A8TLE96TTkHsHDh2yr5LNK2XzatncqlrFp7R2wXy1aFhfwcGuZjLFYUIAAQQQQAABBFIt4OrIx7RiTsuQe3FxcbbxSelq1WUaoxg10zra9Gc4fOAA5cyRw2xiQgABBBDwoACXRgAB5wm4OkA0nPfc4JB7pruaCnXq2e5rTsWcVmhIiF7q+JzWzJ8nMyKKuTYTAggggAACCCAQiAKuDxCTvkPcmsqWzLv3RKtp+w4yHV5v37nT1nnZUo9rzYIP1OGZlsqUKZPdRnI9AhyLAAIIIIAAAv4k4PoA8WpD7plXyN9v/UGTo6LUqfsrKvF0FT0eGalPNnxu6zBvrtx6f9i7mjRsmCLy5LHbSBBAAAEEEEAgUYBZwAr4QYB4qbPqDV9t1Kv9B+q1wW+rzjOtdE+Jknq6YSP1HPCmFixfoT3R+xIqOkgqW7Kk1i1eoHKlSiZsI0UAAQQQQAABBBCwAq4PEE2jkrCQEFuYdt26asrs2Ro/bbq+3LRZsbGxdrvprqbkY4/q+WfbaOrI97Rl3TpNGv6usmTJYveTIODHAhQNAQQQQACB6xZwfYBoShwefpOZ6cKFi3ae87Ycqle9mgb27KGVc6K05dN1mj5qlLq0a6snij+mrFkTjrcHkyCAAAIIIIAAAq4T8GyG/SJAfOj+e61Svjy5NeW9Edr00Uq91ae3GtaqpbsLFbLD5NkDSBBAAAEEEEAAAQSuKeAXAeKEd4dq97eb9cWK5Spdovg1C80BCCCAgBMEyAMCCCDgVAG/CBCdiku+EEAAAQQQQAABNwoQIKap1jgZAQQQQAABBBDwPwECRP+rU0qEAAIIIJBWAc5HIMAFCBAD/AdA8RFAAAEEEEAAgb8KECD+VYR1fxGgHAgggAACCCBwgwIEiDcIx2kIIIAAAggg4AsB7ukNAQJEbyhzDwQQQAABBBBAwEUCBIguqiyyioC/CFAOBBBAAAFnCxAgOrt+yB0CCCCAAAIIIOB1gRsMEL2eT26IAAIIIIAAAggg4CUBAkQvQXMbBBBAwBUCZBIBBBCIFyBAjEfgDwEEEEAAAQQQQOCSAAHiJQt/WaIcCCCAAAIIIIBAmgQIENPEx8kIIIAAAgh4S4D7IOA9AQJE71lzJwQQQAABBBBAwBUCBIiuqCYy6S8ClAMBBBBAAAE3CBAguqGWyCMCCCCAAAIIOFnA7/JGgOh3VUqBEEAAAQQQQACBtAkQIKbNj7MRQMBfBCgHAggggECyAAFiMgULCCCAAAIIIIAAAkbAnwJEUx4mBBBAAAEEEEAAgTQKECCmEZDTEUAAAQQ8LcD1EUDA2wL/DwAA//9by4zXAAAABklEQVQDAJfltel5uKAZAAAAAElFTkSuQmCC</t>
         </is>
       </c>
     </row>
